--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_computer_services.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_computer_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2477566425012664</v>
+        <v>0.2471962265592634</v>
       </c>
       <c r="C2">
-        <v>106.0146085130694</v>
+        <v>105.2790747234343</v>
       </c>
       <c r="D2">
-        <v>104.3846085130694</v>
+        <v>104.6750747234343</v>
       </c>
       <c r="E2">
-        <v>-18.4</v>
+        <v>-17.374</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.026</v>
       </c>
       <c r="G2">
         <v>1.63</v>
@@ -1445,28 +1445,28 @@
         <v>4.34</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0516078</v>
       </c>
       <c r="N2">
-        <v>4.34</v>
+        <v>4.2883922</v>
       </c>
       <c r="O2">
-        <v>1.0416</v>
+        <v>1.029214128</v>
       </c>
       <c r="P2">
-        <v>3.2984</v>
+        <v>3.259178072</v>
       </c>
       <c r="Q2">
-        <v>3.5984</v>
+        <v>3.559178072</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2477566425012664</v>
+        <v>0.2493070167265287</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763957</v>
+        <v>0.9999057154714065</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>84.09581497370553</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2471962265592634</v>
+        <v>0.2466358106172603</v>
       </c>
       <c r="C3">
-        <v>105.2790747234343</v>
+        <v>104.5451619783172</v>
       </c>
       <c r="D3">
-        <v>104.6750747234343</v>
+        <v>104.9671619783172</v>
       </c>
       <c r="E3">
-        <v>-17.374</v>
+        <v>-16.348</v>
       </c>
       <c r="F3">
-        <v>1.026</v>
+        <v>2.052</v>
       </c>
       <c r="G3">
         <v>1.63</v>
@@ -1527,28 +1527,28 @@
         <v>4.34</v>
       </c>
       <c r="M3">
-        <v>0.0516078</v>
+        <v>0.1032156</v>
       </c>
       <c r="N3">
-        <v>4.2883922</v>
+        <v>4.236784399999999</v>
       </c>
       <c r="O3">
-        <v>1.029214128</v>
+        <v>1.016828256</v>
       </c>
       <c r="P3">
-        <v>3.259178072</v>
+        <v>3.219956143999999</v>
       </c>
       <c r="Q3">
-        <v>3.559178072</v>
+        <v>3.519956143999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2493070167265287</v>
+        <v>0.2508890312421023</v>
       </c>
       <c r="T3">
-        <v>0.9999057154714065</v>
+        <v>1.007678741588764</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>84.09581497370553</v>
+        <v>42.04790748685276</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2466358106172603</v>
+        <v>0.2460753946752573</v>
       </c>
       <c r="C4">
-        <v>104.5451619783172</v>
+        <v>103.8128838858678</v>
       </c>
       <c r="D4">
-        <v>104.9671619783172</v>
+        <v>105.2608838858678</v>
       </c>
       <c r="E4">
-        <v>-16.348</v>
+        <v>-15.322</v>
       </c>
       <c r="F4">
-        <v>2.052</v>
+        <v>3.078</v>
       </c>
       <c r="G4">
         <v>1.63</v>
@@ -1609,28 +1609,28 @@
         <v>4.34</v>
       </c>
       <c r="M4">
-        <v>0.1032156</v>
+        <v>0.1548234</v>
       </c>
       <c r="N4">
-        <v>4.236784399999999</v>
+        <v>4.1851766</v>
       </c>
       <c r="O4">
-        <v>1.016828256</v>
+        <v>1.004442384</v>
       </c>
       <c r="P4">
-        <v>3.219956143999999</v>
+        <v>3.180734216</v>
       </c>
       <c r="Q4">
-        <v>3.519956143999999</v>
+        <v>3.480734216</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2508890312421023</v>
+        <v>0.2525036646136673</v>
       </c>
       <c r="T4">
-        <v>1.007678741588764</v>
+        <v>1.015612036285862</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.04790748685276</v>
+        <v>28.03193832456851</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2460753946752573</v>
+        <v>0.2455149787332542</v>
       </c>
       <c r="C5">
-        <v>103.8128838858678</v>
+        <v>103.0822542069781</v>
       </c>
       <c r="D5">
-        <v>105.2608838858678</v>
+        <v>105.5562542069781</v>
       </c>
       <c r="E5">
-        <v>-15.322</v>
+        <v>-14.296</v>
       </c>
       <c r="F5">
-        <v>3.078</v>
+        <v>4.104</v>
       </c>
       <c r="G5">
         <v>1.63</v>
@@ -1691,28 +1691,28 @@
         <v>4.34</v>
       </c>
       <c r="M5">
-        <v>0.1548234</v>
+        <v>0.2064312</v>
       </c>
       <c r="N5">
-        <v>4.1851766</v>
+        <v>4.1335688</v>
       </c>
       <c r="O5">
-        <v>1.004442384</v>
+        <v>0.992056512</v>
       </c>
       <c r="P5">
-        <v>3.180734216</v>
+        <v>3.141512288</v>
       </c>
       <c r="Q5">
-        <v>3.480734216</v>
+        <v>3.441512288</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2525036646136673</v>
+        <v>0.2541519361804732</v>
       </c>
       <c r="T5">
-        <v>1.015612036285862</v>
+        <v>1.023710607955815</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.03193832456851</v>
+        <v>21.02395374342638</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2455149787332542</v>
+        <v>0.2449545627912511</v>
       </c>
       <c r="C6">
-        <v>103.0822542069781</v>
+        <v>102.3532868574312</v>
       </c>
       <c r="D6">
-        <v>105.5562542069781</v>
+        <v>105.8532868574312</v>
       </c>
       <c r="E6">
-        <v>-14.296</v>
+        <v>-13.27</v>
       </c>
       <c r="F6">
-        <v>4.104</v>
+        <v>5.13</v>
       </c>
       <c r="G6">
         <v>1.63</v>
@@ -1773,28 +1773,28 @@
         <v>4.34</v>
       </c>
       <c r="M6">
-        <v>0.2064312</v>
+        <v>0.258039</v>
       </c>
       <c r="N6">
-        <v>4.1335688</v>
+        <v>4.081961</v>
       </c>
       <c r="O6">
-        <v>0.992056512</v>
+        <v>0.9796706399999999</v>
       </c>
       <c r="P6">
-        <v>3.141512288</v>
+        <v>3.10229036</v>
       </c>
       <c r="Q6">
-        <v>3.441512288</v>
+        <v>3.402290359999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2541519361804732</v>
+        <v>0.255834908201317</v>
       </c>
       <c r="T6">
-        <v>1.023710607955815</v>
+        <v>1.031979675871451</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.02395374342638</v>
+        <v>16.81916299474111</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2449545627912511</v>
+        <v>0.2443941468492481</v>
       </c>
       <c r="C7">
-        <v>102.3532868574312</v>
+        <v>101.625995910087</v>
       </c>
       <c r="D7">
-        <v>105.8532868574312</v>
+        <v>106.151995910087</v>
       </c>
       <c r="E7">
-        <v>-13.27</v>
+        <v>-12.244</v>
       </c>
       <c r="F7">
-        <v>5.13</v>
+        <v>6.156000000000001</v>
       </c>
       <c r="G7">
         <v>1.63</v>
@@ -1855,28 +1855,28 @@
         <v>4.34</v>
       </c>
       <c r="M7">
-        <v>0.258039</v>
+        <v>0.3096468</v>
       </c>
       <c r="N7">
-        <v>4.081961</v>
+        <v>4.0303532</v>
       </c>
       <c r="O7">
-        <v>0.9796706399999999</v>
+        <v>0.9672847679999999</v>
       </c>
       <c r="P7">
-        <v>3.10229036</v>
+        <v>3.063068432</v>
       </c>
       <c r="Q7">
-        <v>3.402290359999999</v>
+        <v>3.363068431999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.255834908201317</v>
+        <v>0.257553688137498</v>
       </c>
       <c r="T7">
-        <v>1.031979675871451</v>
+        <v>1.040424681402315</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.81916299474111</v>
+        <v>14.01596916228425</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2443941468492481</v>
+        <v>0.2439135309072451</v>
       </c>
       <c r="C8">
-        <v>101.625995910087</v>
+        <v>100.857516642145</v>
       </c>
       <c r="D8">
-        <v>106.151995910087</v>
+        <v>106.409516642145</v>
       </c>
       <c r="E8">
-        <v>-12.244</v>
+        <v>-11.218</v>
       </c>
       <c r="F8">
-        <v>6.156</v>
+        <v>7.181999999999999</v>
       </c>
       <c r="G8">
         <v>1.63</v>
@@ -1937,45 +1937,45 @@
         <v>4.34</v>
       </c>
       <c r="M8">
-        <v>0.3096467999999999</v>
+        <v>0.3720275999999999</v>
       </c>
       <c r="N8">
-        <v>4.0303532</v>
+        <v>3.9679724</v>
       </c>
       <c r="O8">
-        <v>0.9672847679999999</v>
+        <v>0.9523133759999999</v>
       </c>
       <c r="P8">
-        <v>3.063068432</v>
+        <v>3.015659024</v>
       </c>
       <c r="Q8">
-        <v>3.363068431999999</v>
+        <v>3.315659024</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.257553688137498</v>
+        <v>0.2593094310830593</v>
       </c>
       <c r="T8">
-        <v>1.040424681402315</v>
+        <v>1.049051299955347</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.01596916228426</v>
+        <v>11.66580113948535</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2439135309072451</v>
+        <v>0.2433645149652421</v>
       </c>
       <c r="C9">
-        <v>100.857516642145</v>
+        <v>100.1272201546288</v>
       </c>
       <c r="D9">
-        <v>106.409516642145</v>
+        <v>106.7052201546288</v>
       </c>
       <c r="E9">
-        <v>-11.218</v>
+        <v>-10.192</v>
       </c>
       <c r="F9">
-        <v>7.182</v>
+        <v>8.208</v>
       </c>
       <c r="G9">
         <v>1.63</v>
@@ -2019,28 +2019,28 @@
         <v>4.34</v>
       </c>
       <c r="M9">
-        <v>0.3720276</v>
+        <v>0.4251744</v>
       </c>
       <c r="N9">
-        <v>3.9679724</v>
+        <v>3.9148256</v>
       </c>
       <c r="O9">
-        <v>0.9523133759999999</v>
+        <v>0.9395581439999999</v>
       </c>
       <c r="P9">
-        <v>3.015659024</v>
+        <v>2.975267456</v>
       </c>
       <c r="Q9">
-        <v>3.315659024</v>
+        <v>3.275267456</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2593094310830593</v>
+        <v>0.2611033423535239</v>
       </c>
       <c r="T9">
-        <v>1.049051299955347</v>
+        <v>1.057865453694314</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.66580113948535</v>
+        <v>10.20757599704968</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2433645149652421</v>
+        <v>0.242931779023239</v>
       </c>
       <c r="C10">
-        <v>100.1272201546288</v>
+        <v>99.33545526471124</v>
       </c>
       <c r="D10">
-        <v>106.7052201546288</v>
+        <v>106.9394552647112</v>
       </c>
       <c r="E10">
-        <v>-10.192</v>
+        <v>-9.165999999999999</v>
       </c>
       <c r="F10">
-        <v>8.208</v>
+        <v>9.234</v>
       </c>
       <c r="G10">
         <v>1.63</v>
@@ -2101,45 +2101,45 @@
         <v>4.34</v>
       </c>
       <c r="M10">
-        <v>0.4251744</v>
+        <v>0.494019</v>
       </c>
       <c r="N10">
-        <v>3.9148256</v>
+        <v>3.845981</v>
       </c>
       <c r="O10">
-        <v>0.9395581439999999</v>
+        <v>0.92303544</v>
       </c>
       <c r="P10">
-        <v>2.975267456</v>
+        <v>2.92294556</v>
       </c>
       <c r="Q10">
-        <v>3.275267456</v>
+        <v>3.22294556</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2611033423535239</v>
+        <v>0.2629366802453176</v>
       </c>
       <c r="T10">
-        <v>1.057865453694314</v>
+        <v>1.066873325097874</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.20757599704968</v>
+        <v>8.785087213244836</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.242931779023239</v>
+        <v>0.242395683081236</v>
       </c>
       <c r="C11">
-        <v>99.33545526471124</v>
+        <v>98.60106801586068</v>
       </c>
       <c r="D11">
-        <v>106.9394552647112</v>
+        <v>107.2310680158607</v>
       </c>
       <c r="E11">
-        <v>-9.165999999999999</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="F11">
-        <v>9.234</v>
+        <v>10.26</v>
       </c>
       <c r="G11">
         <v>1.63</v>
@@ -2183,28 +2183,28 @@
         <v>4.34</v>
       </c>
       <c r="M11">
-        <v>0.494019</v>
+        <v>0.5489099999999999</v>
       </c>
       <c r="N11">
-        <v>3.845981</v>
+        <v>3.79109</v>
       </c>
       <c r="O11">
-        <v>0.92303544</v>
+        <v>0.9098615999999999</v>
       </c>
       <c r="P11">
-        <v>2.92294556</v>
+        <v>2.8812284</v>
       </c>
       <c r="Q11">
-        <v>3.22294556</v>
+        <v>3.1812284</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2629366802453176</v>
+        <v>0.2648107589791511</v>
       </c>
       <c r="T11">
-        <v>1.066873325097874</v>
+        <v>1.076081371421514</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.785087213244836</v>
+        <v>7.906578491920353</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.242395683081236</v>
+        <v>0.241926467139233</v>
       </c>
       <c r="C12">
-        <v>98.60106801586066</v>
+        <v>97.8316092533844</v>
       </c>
       <c r="D12">
-        <v>107.2310680158607</v>
+        <v>107.4876092533844</v>
       </c>
       <c r="E12">
-        <v>-8.139999999999999</v>
+        <v>-7.113999999999999</v>
       </c>
       <c r="F12">
-        <v>10.26</v>
+        <v>11.286</v>
       </c>
       <c r="G12">
         <v>1.63</v>
@@ -2265,45 +2265,45 @@
         <v>4.34</v>
       </c>
       <c r="M12">
-        <v>0.54891</v>
+        <v>0.6128298</v>
       </c>
       <c r="N12">
-        <v>3.79109</v>
+        <v>3.7271702</v>
       </c>
       <c r="O12">
-        <v>0.9098615999999998</v>
+        <v>0.8945208479999999</v>
       </c>
       <c r="P12">
-        <v>2.8812284</v>
+        <v>2.832649352</v>
       </c>
       <c r="Q12">
-        <v>3.1812284</v>
+        <v>3.132649352</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2648107589791511</v>
+        <v>0.2667269518418348</v>
       </c>
       <c r="T12">
-        <v>1.076081371421514</v>
+        <v>1.085496340134448</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.24</v>
       </c>
       <c r="W12">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.90657849192035</v>
+        <v>7.081901043323938</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.241926467139233</v>
+        <v>0.2413964511972299</v>
       </c>
       <c r="C13">
-        <v>97.8316092533844</v>
+        <v>97.09687295537582</v>
       </c>
       <c r="D13">
-        <v>107.4876092533844</v>
+        <v>107.7788729553758</v>
       </c>
       <c r="E13">
-        <v>-7.113999999999999</v>
+        <v>-6.087999999999999</v>
       </c>
       <c r="F13">
-        <v>11.286</v>
+        <v>12.312</v>
       </c>
       <c r="G13">
         <v>1.63</v>
@@ -2347,28 +2347,28 @@
         <v>4.34</v>
       </c>
       <c r="M13">
-        <v>0.6128298</v>
+        <v>0.6685416</v>
       </c>
       <c r="N13">
-        <v>3.7271702</v>
+        <v>3.6714584</v>
       </c>
       <c r="O13">
-        <v>0.8945208479999999</v>
+        <v>0.8811500159999999</v>
       </c>
       <c r="P13">
-        <v>2.832649352</v>
+        <v>2.790308384</v>
       </c>
       <c r="Q13">
-        <v>3.132649352</v>
+        <v>3.090308384</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2667269518418348</v>
+        <v>0.2686866945423067</v>
       </c>
       <c r="T13">
-        <v>1.085496340134448</v>
+        <v>1.09512528540904</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.081901043323938</v>
+        <v>6.491742623046942</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2413964511972299</v>
+        <v>0.2409652352552269</v>
       </c>
       <c r="C14">
-        <v>97.09687295537582</v>
+        <v>96.30900946656696</v>
       </c>
       <c r="D14">
-        <v>107.7788729553758</v>
+        <v>108.017009466567</v>
       </c>
       <c r="E14">
-        <v>-6.087999999999999</v>
+        <v>-5.061999999999999</v>
       </c>
       <c r="F14">
-        <v>12.312</v>
+        <v>13.338</v>
       </c>
       <c r="G14">
         <v>1.63</v>
@@ -2429,45 +2429,45 @@
         <v>4.34</v>
       </c>
       <c r="M14">
-        <v>0.6685416</v>
+        <v>0.7375914</v>
       </c>
       <c r="N14">
-        <v>3.6714584</v>
+        <v>3.6024086</v>
       </c>
       <c r="O14">
-        <v>0.8811500159999999</v>
+        <v>0.8645780639999999</v>
       </c>
       <c r="P14">
-        <v>2.790308384</v>
+        <v>2.737830536</v>
       </c>
       <c r="Q14">
-        <v>3.090308384</v>
+        <v>3.037830536</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2686866945423067</v>
+        <v>0.2706914887991114</v>
       </c>
       <c r="T14">
-        <v>1.09512528540904</v>
+        <v>1.104975585747416</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.24</v>
       </c>
       <c r="W14">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.491742623046942</v>
+        <v>5.884016543576837</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2409652352552269</v>
+        <v>0.2404428193132238</v>
       </c>
       <c r="C15">
-        <v>96.30900946656696</v>
+        <v>95.57292413155143</v>
       </c>
       <c r="D15">
-        <v>108.017009466567</v>
+        <v>108.3069241315514</v>
       </c>
       <c r="E15">
-        <v>-5.061999999999999</v>
+        <v>-4.035999999999998</v>
       </c>
       <c r="F15">
-        <v>13.338</v>
+        <v>14.364</v>
       </c>
       <c r="G15">
         <v>1.63</v>
@@ -2511,28 +2511,28 @@
         <v>4.34</v>
       </c>
       <c r="M15">
-        <v>0.7375914</v>
+        <v>0.7943292000000001</v>
       </c>
       <c r="N15">
-        <v>3.6024086</v>
+        <v>3.5456708</v>
       </c>
       <c r="O15">
-        <v>0.8645780639999999</v>
+        <v>0.850960992</v>
       </c>
       <c r="P15">
-        <v>2.737830536</v>
+        <v>2.694709808</v>
       </c>
       <c r="Q15">
-        <v>3.037830536</v>
+        <v>2.994709808</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2706914887991114</v>
+        <v>0.2727429061781672</v>
       </c>
       <c r="T15">
-        <v>1.104975585747416</v>
+        <v>1.115054962837847</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.884016543576837</v>
+        <v>5.463729647607062</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2404428193132238</v>
+        <v>0.2399204033712208</v>
       </c>
       <c r="C16">
-        <v>95.57292413155143</v>
+        <v>94.83839923057764</v>
       </c>
       <c r="D16">
-        <v>108.3069241315514</v>
+        <v>108.5983992305776</v>
       </c>
       <c r="E16">
-        <v>-4.035999999999998</v>
+        <v>-3.009999999999998</v>
       </c>
       <c r="F16">
-        <v>14.364</v>
+        <v>15.39</v>
       </c>
       <c r="G16">
         <v>1.63</v>
@@ -2593,28 +2593,28 @@
         <v>4.34</v>
       </c>
       <c r="M16">
-        <v>0.7943292000000001</v>
+        <v>0.851067</v>
       </c>
       <c r="N16">
-        <v>3.5456708</v>
+        <v>3.488933</v>
       </c>
       <c r="O16">
-        <v>0.850960992</v>
+        <v>0.8373439199999999</v>
       </c>
       <c r="P16">
-        <v>2.694709808</v>
+        <v>2.65158908</v>
       </c>
       <c r="Q16">
-        <v>2.994709808</v>
+        <v>2.95158908</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2727429061781672</v>
+        <v>0.2748425922014363</v>
       </c>
       <c r="T16">
-        <v>1.115054962837847</v>
+        <v>1.125371501742171</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.463729647607062</v>
+        <v>5.099481004433258</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2399204033712208</v>
+        <v>0.2393979874292177</v>
       </c>
       <c r="C17">
-        <v>94.83839923057765</v>
+        <v>94.10544739594047</v>
       </c>
       <c r="D17">
-        <v>108.5983992305777</v>
+        <v>108.8914473959405</v>
       </c>
       <c r="E17">
-        <v>-3.01</v>
+        <v>-1.983999999999998</v>
       </c>
       <c r="F17">
-        <v>15.39</v>
+        <v>16.416</v>
       </c>
       <c r="G17">
         <v>1.63</v>
@@ -2675,28 +2675,28 @@
         <v>4.34</v>
       </c>
       <c r="M17">
-        <v>0.851067</v>
+        <v>0.9078048000000001</v>
       </c>
       <c r="N17">
-        <v>3.488933</v>
+        <v>3.4321952</v>
       </c>
       <c r="O17">
-        <v>0.8373439199999999</v>
+        <v>0.823726848</v>
       </c>
       <c r="P17">
-        <v>2.65158908</v>
+        <v>2.608468352</v>
       </c>
       <c r="Q17">
-        <v>2.95158908</v>
+        <v>2.908468352</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2748425922014362</v>
+        <v>0.2769922707490687</v>
       </c>
       <c r="T17">
-        <v>1.125371501742171</v>
+        <v>1.135933672525169</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.099481004433258</v>
+        <v>4.780763441656179</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2393979874292177</v>
+        <v>0.2391985714872147</v>
       </c>
       <c r="C18">
-        <v>94.10544739594047</v>
+        <v>93.19172687345446</v>
       </c>
       <c r="D18">
-        <v>108.8914473959405</v>
+        <v>109.0037268734545</v>
       </c>
       <c r="E18">
-        <v>-1.983999999999998</v>
+        <v>-0.9579999999999984</v>
       </c>
       <c r="F18">
-        <v>16.416</v>
+        <v>17.442</v>
       </c>
       <c r="G18">
         <v>1.63</v>
@@ -2757,45 +2757,45 @@
         <v>4.34</v>
       </c>
       <c r="M18">
-        <v>0.9078048000000001</v>
+        <v>1.0081476</v>
       </c>
       <c r="N18">
-        <v>3.4321952</v>
+        <v>3.3318524</v>
       </c>
       <c r="O18">
-        <v>0.823726848</v>
+        <v>0.7996445759999999</v>
       </c>
       <c r="P18">
-        <v>2.608468352</v>
+        <v>2.532207824</v>
       </c>
       <c r="Q18">
-        <v>2.908468352</v>
+        <v>2.832207824</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2769922707490687</v>
+        <v>0.2791937487797768</v>
       </c>
       <c r="T18">
-        <v>1.135933672525169</v>
+        <v>1.146750353447517</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.780763441656179</v>
+        <v>4.304925191509655</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2391985714872147</v>
+        <v>0.2386951555452117</v>
       </c>
       <c r="C19">
-        <v>93.19172687345446</v>
+        <v>92.45020376293745</v>
       </c>
       <c r="D19">
-        <v>109.0037268734545</v>
+        <v>109.2882037629375</v>
       </c>
       <c r="E19">
-        <v>-0.9579999999999984</v>
+        <v>0.06800000000000139</v>
       </c>
       <c r="F19">
-        <v>17.442</v>
+        <v>18.468</v>
       </c>
       <c r="G19">
         <v>1.63</v>
@@ -2839,28 +2839,28 @@
         <v>4.34</v>
       </c>
       <c r="M19">
-        <v>1.0081476</v>
+        <v>1.0674504</v>
       </c>
       <c r="N19">
-        <v>3.3318524</v>
+        <v>3.2725496</v>
       </c>
       <c r="O19">
-        <v>0.7996445759999999</v>
+        <v>0.7854119039999998</v>
       </c>
       <c r="P19">
-        <v>2.532207824</v>
+        <v>2.487137696</v>
       </c>
       <c r="Q19">
-        <v>2.832207824</v>
+        <v>2.787137695999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2791937487797768</v>
+        <v>0.2814489213965996</v>
       </c>
       <c r="T19">
-        <v>1.146750353447517</v>
+        <v>1.157830855855775</v>
       </c>
       <c r="U19">
         <v>0.0578</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.304925191509655</v>
+        <v>4.065762680870231</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2386951555452117</v>
+        <v>0.2386971396032087</v>
       </c>
       <c r="C20">
-        <v>92.45020376293742</v>
+        <v>91.42307967092084</v>
       </c>
       <c r="D20">
-        <v>109.2882037629374</v>
+        <v>109.2870796709208</v>
       </c>
       <c r="E20">
-        <v>0.06800000000000139</v>
+        <v>1.094000000000001</v>
       </c>
       <c r="F20">
-        <v>18.468</v>
+        <v>19.494</v>
       </c>
       <c r="G20">
         <v>1.63</v>
@@ -2921,45 +2921,45 @@
         <v>4.34</v>
       </c>
       <c r="M20">
-        <v>1.0674504</v>
+        <v>1.1949822</v>
       </c>
       <c r="N20">
-        <v>3.2725496</v>
+        <v>3.1450178</v>
       </c>
       <c r="O20">
-        <v>0.7854119039999998</v>
+        <v>0.7548042719999999</v>
       </c>
       <c r="P20">
-        <v>2.487137696</v>
+        <v>2.390213528</v>
       </c>
       <c r="Q20">
-        <v>2.787137695999999</v>
+        <v>2.690213528</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2814489213965996</v>
+        <v>0.2837597772879119</v>
       </c>
       <c r="T20">
-        <v>1.157830855855775</v>
+        <v>1.169184950916089</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.065762680870231</v>
+        <v>3.631853261077864</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2386971396032087</v>
+        <v>0.2386459236612056</v>
       </c>
       <c r="C21">
-        <v>91.42307967092084</v>
+        <v>90.42610408910843</v>
       </c>
       <c r="D21">
-        <v>109.2870796709208</v>
+        <v>109.3161040891084</v>
       </c>
       <c r="E21">
-        <v>1.094000000000001</v>
+        <v>2.120000000000001</v>
       </c>
       <c r="F21">
-        <v>19.494</v>
+        <v>20.52</v>
       </c>
       <c r="G21">
         <v>1.63</v>
@@ -3003,45 +3003,45 @@
         <v>4.34</v>
       </c>
       <c r="M21">
-        <v>1.1949822</v>
+        <v>1.315332</v>
       </c>
       <c r="N21">
-        <v>3.1450178</v>
+        <v>3.024668</v>
       </c>
       <c r="O21">
-        <v>0.7548042719999999</v>
+        <v>0.72592032</v>
       </c>
       <c r="P21">
-        <v>2.390213528</v>
+        <v>2.29874768</v>
       </c>
       <c r="Q21">
-        <v>2.690213528</v>
+        <v>2.59874768</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2837597772879119</v>
+        <v>0.286128404576507</v>
       </c>
       <c r="T21">
-        <v>1.169184950916089</v>
+        <v>1.180822898352911</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.631853261077864</v>
+        <v>3.299547186565825</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2386459236612056</v>
+        <v>0.2381903877192025</v>
       </c>
       <c r="C22">
-        <v>90.42610408910843</v>
+        <v>89.65893934092472</v>
       </c>
       <c r="D22">
-        <v>109.3161040891084</v>
+        <v>109.5749393409247</v>
       </c>
       <c r="E22">
-        <v>2.120000000000001</v>
+        <v>3.146000000000001</v>
       </c>
       <c r="F22">
-        <v>20.52</v>
+        <v>21.546</v>
       </c>
       <c r="G22">
         <v>1.63</v>
@@ -3085,28 +3085,28 @@
         <v>4.34</v>
       </c>
       <c r="M22">
-        <v>1.315332</v>
+        <v>1.3810986</v>
       </c>
       <c r="N22">
-        <v>3.024668</v>
+        <v>2.9589014</v>
       </c>
       <c r="O22">
-        <v>0.72592032</v>
+        <v>0.7101363359999999</v>
       </c>
       <c r="P22">
-        <v>2.29874768</v>
+        <v>2.248765064</v>
       </c>
       <c r="Q22">
-        <v>2.59874768</v>
+        <v>2.548765063999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.286128404576507</v>
+        <v>0.2885569971129146</v>
       </c>
       <c r="T22">
-        <v>1.180822898352911</v>
+        <v>1.192755477370412</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.299547186565825</v>
+        <v>3.142425891967452</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2381903877192025</v>
+        <v>0.2390390117771995</v>
       </c>
       <c r="C23">
-        <v>89.65893934092472</v>
+        <v>88.1517325244384</v>
       </c>
       <c r="D23">
-        <v>109.5749393409247</v>
+        <v>109.0937325244384</v>
       </c>
       <c r="E23">
-        <v>3.146000000000001</v>
+        <v>4.172000000000001</v>
       </c>
       <c r="F23">
-        <v>21.546</v>
+        <v>22.572</v>
       </c>
       <c r="G23">
         <v>1.63</v>
@@ -3167,45 +3167,45 @@
         <v>4.34</v>
       </c>
       <c r="M23">
-        <v>1.3810986</v>
+        <v>1.6229268</v>
       </c>
       <c r="N23">
-        <v>2.9589014</v>
+        <v>2.7170732</v>
       </c>
       <c r="O23">
-        <v>0.7101363359999999</v>
+        <v>0.652097568</v>
       </c>
       <c r="P23">
-        <v>2.248765064</v>
+        <v>2.064975632</v>
       </c>
       <c r="Q23">
-        <v>2.548765063999999</v>
+        <v>2.364975632</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2885569971129146</v>
+        <v>0.2910478612528199</v>
       </c>
       <c r="T23">
-        <v>1.192755477370412</v>
+        <v>1.204994019952464</v>
       </c>
       <c r="U23">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.142425891967452</v>
+        <v>2.674180992020096</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2390390117771995</v>
+        <v>0.2386427558351965</v>
       </c>
       <c r="C24">
-        <v>88.1517325244384</v>
+        <v>87.34989982364999</v>
       </c>
       <c r="D24">
-        <v>109.0937325244384</v>
+        <v>109.31789982365</v>
       </c>
       <c r="E24">
-        <v>4.172000000000001</v>
+        <v>5.198</v>
       </c>
       <c r="F24">
-        <v>22.572</v>
+        <v>23.598</v>
       </c>
       <c r="G24">
         <v>1.63</v>
@@ -3249,28 +3249,28 @@
         <v>4.34</v>
       </c>
       <c r="M24">
-        <v>1.6229268</v>
+        <v>1.6966962</v>
       </c>
       <c r="N24">
-        <v>2.7170732</v>
+        <v>2.6433038</v>
       </c>
       <c r="O24">
-        <v>0.652097568</v>
+        <v>0.6343929119999999</v>
       </c>
       <c r="P24">
-        <v>2.064975632</v>
+        <v>2.008910888</v>
       </c>
       <c r="Q24">
-        <v>2.364975632</v>
+        <v>2.308910888</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2910478612528199</v>
+        <v>0.2936034231625929</v>
       </c>
       <c r="T24">
-        <v>1.204994019952464</v>
+        <v>1.217550446757427</v>
       </c>
       <c r="U24">
         <v>0.07190000000000001</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.674180992020096</v>
+        <v>2.557912253236613</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2386427558351965</v>
+        <v>0.2389578598931934</v>
       </c>
       <c r="C25">
-        <v>87.34989982364999</v>
+        <v>86.14556634105097</v>
       </c>
       <c r="D25">
-        <v>109.31789982365</v>
+        <v>109.139566341051</v>
       </c>
       <c r="E25">
-        <v>5.198</v>
+        <v>6.224000000000004</v>
       </c>
       <c r="F25">
-        <v>23.598</v>
+        <v>24.624</v>
       </c>
       <c r="G25">
         <v>1.63</v>
@@ -3331,45 +3331,45 @@
         <v>4.34</v>
       </c>
       <c r="M25">
-        <v>1.6966962</v>
+        <v>1.8664992</v>
       </c>
       <c r="N25">
-        <v>2.6433038</v>
+        <v>2.4735008</v>
       </c>
       <c r="O25">
-        <v>0.6343929119999999</v>
+        <v>0.5936401919999998</v>
       </c>
       <c r="P25">
-        <v>2.008910888</v>
+        <v>1.879860608</v>
       </c>
       <c r="Q25">
-        <v>2.308910888</v>
+        <v>2.179860607999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2936034231625929</v>
+        <v>0.2962262367015703</v>
       </c>
       <c r="T25">
-        <v>1.217550446757427</v>
+        <v>1.230437305846731</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.557912253236613</v>
+        <v>2.325208604429083</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2389578598931934</v>
+        <v>0.2385912439511904</v>
       </c>
       <c r="C26">
-        <v>86.14556634105097</v>
+        <v>85.32710846850387</v>
       </c>
       <c r="D26">
-        <v>109.139566341051</v>
+        <v>109.3471084685039</v>
       </c>
       <c r="E26">
-        <v>6.224</v>
+        <v>7.25</v>
       </c>
       <c r="F26">
-        <v>24.624</v>
+        <v>25.65</v>
       </c>
       <c r="G26">
         <v>1.63</v>
@@ -3413,28 +3413,28 @@
         <v>4.34</v>
       </c>
       <c r="M26">
-        <v>1.8664992</v>
+        <v>1.94427</v>
       </c>
       <c r="N26">
-        <v>2.4735008</v>
+        <v>2.39573</v>
       </c>
       <c r="O26">
-        <v>0.593640192</v>
+        <v>0.5749751999999999</v>
       </c>
       <c r="P26">
-        <v>1.879860608</v>
+        <v>1.8207548</v>
       </c>
       <c r="Q26">
-        <v>2.179860608</v>
+        <v>2.1207548</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2962262367015703</v>
+        <v>0.2989189919349206</v>
       </c>
       <c r="T26">
-        <v>1.230437305846731</v>
+        <v>1.243667814511749</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.325208604429083</v>
+        <v>2.23220026025192</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2385912439511904</v>
+        <v>0.2382246280091873</v>
       </c>
       <c r="C27">
-        <v>85.32710846850387</v>
+        <v>84.50944143290268</v>
       </c>
       <c r="D27">
-        <v>109.3471084685039</v>
+        <v>109.5554414329027</v>
       </c>
       <c r="E27">
-        <v>7.25</v>
+        <v>8.276</v>
       </c>
       <c r="F27">
-        <v>25.65</v>
+        <v>26.676</v>
       </c>
       <c r="G27">
         <v>1.63</v>
@@ -3495,28 +3495,28 @@
         <v>4.34</v>
       </c>
       <c r="M27">
-        <v>1.94427</v>
+        <v>2.0220408</v>
       </c>
       <c r="N27">
-        <v>2.39573</v>
+        <v>2.3179592</v>
       </c>
       <c r="O27">
-        <v>0.5749751999999999</v>
+        <v>0.556310208</v>
       </c>
       <c r="P27">
-        <v>1.8207548</v>
+        <v>1.761648992</v>
       </c>
       <c r="Q27">
-        <v>2.1207548</v>
+        <v>2.061648991999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2989189919349206</v>
+        <v>0.3016845243367396</v>
       </c>
       <c r="T27">
-        <v>1.243667814511749</v>
+        <v>1.257255904492039</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.23220026025192</v>
+        <v>2.146346404088384</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2382246280091873</v>
+        <v>0.2378580120671843</v>
       </c>
       <c r="C28">
-        <v>84.50944143290268</v>
+        <v>83.69256976308884</v>
       </c>
       <c r="D28">
-        <v>109.5554414329027</v>
+        <v>109.7645697630888</v>
       </c>
       <c r="E28">
-        <v>8.276</v>
+        <v>9.302000000000003</v>
       </c>
       <c r="F28">
-        <v>26.676</v>
+        <v>27.702</v>
       </c>
       <c r="G28">
         <v>1.63</v>
@@ -3577,28 +3577,28 @@
         <v>4.34</v>
       </c>
       <c r="M28">
-        <v>2.0220408</v>
+        <v>2.0998116</v>
       </c>
       <c r="N28">
-        <v>2.3179592</v>
+        <v>2.2401884</v>
       </c>
       <c r="O28">
-        <v>0.556310208</v>
+        <v>0.5376452159999999</v>
       </c>
       <c r="P28">
-        <v>1.761648992</v>
+        <v>1.702543184</v>
       </c>
       <c r="Q28">
-        <v>2.061648991999999</v>
+        <v>2.002543183999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.3016845243367396</v>
+        <v>0.3045258247495675</v>
       </c>
       <c r="T28">
-        <v>1.257255904492039</v>
+        <v>1.271216270910144</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.146346404088384</v>
+        <v>2.066852092825851</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2378580120671843</v>
+        <v>0.2405131561251813</v>
       </c>
       <c r="C29">
-        <v>83.69256976308884</v>
+        <v>81.16980009952437</v>
       </c>
       <c r="D29">
-        <v>109.7645697630888</v>
+        <v>108.2678000995244</v>
       </c>
       <c r="E29">
-        <v>9.302000000000003</v>
+        <v>10.328</v>
       </c>
       <c r="F29">
-        <v>27.702</v>
+        <v>28.728</v>
       </c>
       <c r="G29">
         <v>1.63</v>
@@ -3659,45 +3659,45 @@
         <v>4.34</v>
       </c>
       <c r="M29">
-        <v>2.0998116</v>
+        <v>2.58552</v>
       </c>
       <c r="N29">
-        <v>2.2401884</v>
+        <v>1.75448</v>
       </c>
       <c r="O29">
-        <v>0.5376452159999999</v>
+        <v>0.4210751999999999</v>
       </c>
       <c r="P29">
-        <v>1.702543184</v>
+        <v>1.3334048</v>
       </c>
       <c r="Q29">
-        <v>2.002543183999999</v>
+        <v>1.6334048</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.3045258247495675</v>
+        <v>0.3074460501738629</v>
       </c>
       <c r="T29">
-        <v>1.271216270910144</v>
+        <v>1.285564425284308</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.066852092825851</v>
+        <v>1.678579163959281</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2405131561251813</v>
+        <v>0.2402544601831783</v>
       </c>
       <c r="C30">
-        <v>81.16980009952437</v>
+        <v>80.2878360887681</v>
       </c>
       <c r="D30">
-        <v>108.2678000995244</v>
+        <v>108.4118360887681</v>
       </c>
       <c r="E30">
-        <v>10.328</v>
+        <v>11.354</v>
       </c>
       <c r="F30">
-        <v>28.728</v>
+        <v>29.754</v>
       </c>
       <c r="G30">
         <v>1.63</v>
@@ -3741,28 +3741,28 @@
         <v>4.34</v>
       </c>
       <c r="M30">
-        <v>2.58552</v>
+        <v>2.67786</v>
       </c>
       <c r="N30">
-        <v>1.75448</v>
+        <v>1.66214</v>
       </c>
       <c r="O30">
-        <v>0.4210751999999999</v>
+        <v>0.3989136</v>
       </c>
       <c r="P30">
-        <v>1.3334048</v>
+        <v>1.2632264</v>
       </c>
       <c r="Q30">
-        <v>1.6334048</v>
+        <v>1.5632264</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.3074460501738629</v>
+        <v>0.3104485354692652</v>
       </c>
       <c r="T30">
-        <v>1.285564425284308</v>
+        <v>1.300316753021125</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.678579163959281</v>
+        <v>1.620697123822754</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2402544601831783</v>
+        <v>0.2399957642411752</v>
       </c>
       <c r="C31">
-        <v>80.2878360887681</v>
+        <v>79.40625583021229</v>
       </c>
       <c r="D31">
-        <v>108.4118360887681</v>
+        <v>108.5562558302123</v>
       </c>
       <c r="E31">
-        <v>11.354</v>
+        <v>12.38</v>
       </c>
       <c r="F31">
-        <v>29.754</v>
+        <v>30.78</v>
       </c>
       <c r="G31">
         <v>1.63</v>
@@ -3823,28 +3823,28 @@
         <v>4.34</v>
       </c>
       <c r="M31">
-        <v>2.67786</v>
+        <v>2.7702</v>
       </c>
       <c r="N31">
-        <v>1.66214</v>
+        <v>1.5698</v>
       </c>
       <c r="O31">
-        <v>0.3989136</v>
+        <v>0.3767520000000001</v>
       </c>
       <c r="P31">
-        <v>1.2632264</v>
+        <v>1.193048</v>
       </c>
       <c r="Q31">
-        <v>1.5632264</v>
+        <v>1.493048</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.3104485354692652</v>
+        <v>0.3135368060588217</v>
       </c>
       <c r="T31">
-        <v>1.300316753021125</v>
+        <v>1.315490575836136</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.620697123822754</v>
+        <v>1.566673886361996</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2399957642411752</v>
+        <v>0.2397370682991722</v>
       </c>
       <c r="C32">
-        <v>79.40625583021229</v>
+        <v>78.52506085953756</v>
       </c>
       <c r="D32">
-        <v>108.5562558302123</v>
+        <v>108.7010608595376</v>
       </c>
       <c r="E32">
-        <v>12.38</v>
+        <v>13.406</v>
       </c>
       <c r="F32">
-        <v>30.78</v>
+        <v>31.806</v>
       </c>
       <c r="G32">
         <v>1.63</v>
@@ -3905,28 +3905,28 @@
         <v>4.34</v>
       </c>
       <c r="M32">
-        <v>2.7702</v>
+        <v>2.86254</v>
       </c>
       <c r="N32">
-        <v>1.5698</v>
+        <v>1.47746</v>
       </c>
       <c r="O32">
-        <v>0.3767520000000001</v>
+        <v>0.3545904</v>
       </c>
       <c r="P32">
-        <v>1.193048</v>
+        <v>1.1228696</v>
       </c>
       <c r="Q32">
-        <v>1.493048</v>
+        <v>1.4228696</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.3135368060588217</v>
+        <v>0.3167145917379307</v>
       </c>
       <c r="T32">
-        <v>1.315490575836136</v>
+        <v>1.331104219602307</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.566673886361996</v>
+        <v>1.516136019059996</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2397370682991722</v>
+        <v>0.2559581564605777</v>
       </c>
       <c r="C33">
-        <v>78.52506085953756</v>
+        <v>69.10895351782403</v>
       </c>
       <c r="D33">
-        <v>108.7010608595376</v>
+        <v>100.310953517824</v>
       </c>
       <c r="E33">
-        <v>13.406</v>
+        <v>14.432</v>
       </c>
       <c r="F33">
-        <v>31.806</v>
+        <v>32.832</v>
       </c>
       <c r="G33">
         <v>1.63</v>
@@ -3987,45 +3987,45 @@
         <v>4.34</v>
       </c>
       <c r="M33">
-        <v>2.86254</v>
+        <v>4.819737600000001</v>
       </c>
       <c r="N33">
-        <v>1.47746</v>
+        <v>-0.4797376000000009</v>
       </c>
       <c r="O33">
-        <v>0.3545904</v>
+        <v>-0.1151370240000002</v>
       </c>
       <c r="P33">
-        <v>1.1228696</v>
+        <v>-0.3646005760000007</v>
       </c>
       <c r="Q33">
-        <v>1.4228696</v>
+        <v>-0.06460057600000085</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.3167145917379307</v>
+        <v>0.3222561812414757</v>
       </c>
       <c r="T33">
-        <v>1.331104219602307</v>
+        <v>1.358332111330665</v>
       </c>
       <c r="U33">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.24</v>
+        <v>0.2161113501282725</v>
       </c>
       <c r="W33">
-        <v>0.0684</v>
+        <v>0.1150748538011696</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.516136019059996</v>
+        <v>0.9004639588678021</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2559581564605777</v>
+        <v>0.2569681564605777</v>
       </c>
       <c r="C34">
-        <v>69.10895351782403</v>
+        <v>67.60317444151281</v>
       </c>
       <c r="D34">
-        <v>100.310953517824</v>
+        <v>99.83117444151281</v>
       </c>
       <c r="E34">
-        <v>14.432</v>
+        <v>15.458</v>
       </c>
       <c r="F34">
-        <v>32.832</v>
+        <v>33.858</v>
       </c>
       <c r="G34">
         <v>1.63</v>
@@ -4069,37 +4069,37 @@
         <v>4.34</v>
       </c>
       <c r="M34">
-        <v>4.819737600000001</v>
+        <v>4.9703544</v>
       </c>
       <c r="N34">
-        <v>-0.4797376000000009</v>
+        <v>-0.6303543999999999</v>
       </c>
       <c r="O34">
-        <v>-0.1151370240000002</v>
+        <v>-0.151285056</v>
       </c>
       <c r="P34">
-        <v>-0.3646005760000007</v>
+        <v>-0.4790693439999999</v>
       </c>
       <c r="Q34">
-        <v>-0.06460057600000085</v>
+        <v>-0.1790693440000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3222561812414757</v>
+        <v>0.3263823929017963</v>
       </c>
       <c r="T34">
-        <v>1.358332111330665</v>
+        <v>1.378605724932615</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2161113501282725</v>
+        <v>0.2095625213365067</v>
       </c>
       <c r="W34">
-        <v>0.1150748538011696</v>
+        <v>0.1160362218678008</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9004639588678021</v>
+        <v>0.8731771722354447</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2569681564605777</v>
+        <v>0.2579781564605778</v>
       </c>
       <c r="C35">
-        <v>67.60317444151281</v>
+        <v>66.10196300661346</v>
       </c>
       <c r="D35">
-        <v>99.83117444151281</v>
+        <v>99.35596300661346</v>
       </c>
       <c r="E35">
-        <v>15.458</v>
+        <v>16.484</v>
       </c>
       <c r="F35">
-        <v>33.858</v>
+        <v>34.884</v>
       </c>
       <c r="G35">
         <v>1.63</v>
@@ -4151,37 +4151,37 @@
         <v>4.34</v>
       </c>
       <c r="M35">
-        <v>4.9703544</v>
+        <v>5.120971200000001</v>
       </c>
       <c r="N35">
-        <v>-0.6303543999999999</v>
+        <v>-0.7809712000000006</v>
       </c>
       <c r="O35">
-        <v>-0.151285056</v>
+        <v>-0.1874330880000001</v>
       </c>
       <c r="P35">
-        <v>-0.4790693439999999</v>
+        <v>-0.5935381120000005</v>
       </c>
       <c r="Q35">
-        <v>-0.1790693440000001</v>
+        <v>-0.2935381120000007</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3263823929017963</v>
+        <v>0.3306336412790962</v>
       </c>
       <c r="T35">
-        <v>1.378605724932615</v>
+        <v>1.399493690461897</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2095625213365067</v>
+        <v>0.2033989177677859</v>
       </c>
       <c r="W35">
-        <v>0.1160362218678008</v>
+        <v>0.1169410388716891</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8731771722354447</v>
+        <v>0.8474954906991079</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2579781564605778</v>
+        <v>0.2589881564605778</v>
       </c>
       <c r="C36">
-        <v>66.10196300661346</v>
+        <v>64.60525429416563</v>
       </c>
       <c r="D36">
-        <v>99.35596300661346</v>
+        <v>98.88525429416565</v>
       </c>
       <c r="E36">
-        <v>16.484</v>
+        <v>17.51000000000001</v>
       </c>
       <c r="F36">
-        <v>34.884</v>
+        <v>35.91</v>
       </c>
       <c r="G36">
         <v>1.63</v>
@@ -4233,37 +4233,37 @@
         <v>4.34</v>
       </c>
       <c r="M36">
-        <v>5.120971200000001</v>
+        <v>5.271588000000001</v>
       </c>
       <c r="N36">
-        <v>-0.7809712000000006</v>
+        <v>-0.9315880000000014</v>
       </c>
       <c r="O36">
-        <v>-0.1874330880000001</v>
+        <v>-0.2235811200000003</v>
       </c>
       <c r="P36">
-        <v>-0.5935381120000005</v>
+        <v>-0.7080068800000011</v>
       </c>
       <c r="Q36">
-        <v>-0.2935381120000007</v>
+        <v>-0.4080068800000013</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3306336412790962</v>
+        <v>0.3350156972987746</v>
       </c>
       <c r="T36">
-        <v>1.399493690461897</v>
+        <v>1.42102436262285</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.2033989177677859</v>
+        <v>0.1975875201172777</v>
       </c>
       <c r="W36">
-        <v>0.1169410388716891</v>
+        <v>0.1177941520467836</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8474954906991079</v>
+        <v>0.8232813338219904</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2589881564605778</v>
+        <v>0.2599981564605777</v>
       </c>
       <c r="C37">
-        <v>64.60525429416563</v>
+        <v>63.11298460964816</v>
       </c>
       <c r="D37">
-        <v>98.88525429416565</v>
+        <v>98.41898460964816</v>
       </c>
       <c r="E37">
-        <v>17.51000000000001</v>
+        <v>18.536</v>
       </c>
       <c r="F37">
-        <v>35.91</v>
+        <v>36.936</v>
       </c>
       <c r="G37">
         <v>1.63</v>
@@ -4315,37 +4315,37 @@
         <v>4.34</v>
       </c>
       <c r="M37">
-        <v>5.271588000000001</v>
+        <v>5.4222048</v>
       </c>
       <c r="N37">
-        <v>-0.9315880000000014</v>
+        <v>-1.0822048</v>
       </c>
       <c r="O37">
-        <v>-0.2235811200000003</v>
+        <v>-0.2597291520000001</v>
       </c>
       <c r="P37">
-        <v>-0.7080068800000011</v>
+        <v>-0.8224756480000004</v>
       </c>
       <c r="Q37">
-        <v>-0.4080068800000013</v>
+        <v>-0.5224756480000006</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3350156972987746</v>
+        <v>0.3395346925690679</v>
       </c>
       <c r="T37">
-        <v>1.42102436262285</v>
+        <v>1.443227868288832</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1975875201172777</v>
+        <v>0.1920989778917978</v>
       </c>
       <c r="W37">
-        <v>0.1177941520467836</v>
+        <v>0.1185998700454841</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8232813338219904</v>
+        <v>0.8004124078824908</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2599981564605778</v>
+        <v>0.2847440714002262</v>
       </c>
       <c r="C38">
-        <v>63.11298460964813</v>
+        <v>51.89435749266242</v>
       </c>
       <c r="D38">
-        <v>98.41898460964813</v>
+        <v>88.22635749266242</v>
       </c>
       <c r="E38">
-        <v>18.536</v>
+        <v>19.562</v>
       </c>
       <c r="F38">
-        <v>36.936</v>
+        <v>37.962</v>
       </c>
       <c r="G38">
         <v>1.63</v>
@@ -4397,45 +4397,45 @@
         <v>4.34</v>
       </c>
       <c r="M38">
-        <v>5.4222048</v>
+        <v>7.6227696</v>
       </c>
       <c r="N38">
-        <v>-1.0822048</v>
+        <v>-3.2827696</v>
       </c>
       <c r="O38">
-        <v>-0.2597291520000001</v>
+        <v>-0.787864704</v>
       </c>
       <c r="P38">
-        <v>-0.8224756480000004</v>
+        <v>-2.494904896</v>
       </c>
       <c r="Q38">
-        <v>-0.5224756480000006</v>
+        <v>-2.194904896</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3395346925690679</v>
+        <v>0.3501589177521459</v>
       </c>
       <c r="T38">
-        <v>1.443227868288832</v>
+        <v>1.495428640792368</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1920989778917978</v>
+        <v>0.1366432484067208</v>
       </c>
       <c r="W38">
-        <v>0.1185998700454841</v>
+        <v>0.1733620357199305</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8004124078824908</v>
+        <v>0.5693468683613367</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2847440714002262</v>
+        <v>0.2862940714002261</v>
       </c>
       <c r="C39">
-        <v>51.89435749266242</v>
+        <v>50.29973285540038</v>
       </c>
       <c r="D39">
-        <v>88.22635749266242</v>
+        <v>87.65773285540038</v>
       </c>
       <c r="E39">
-        <v>19.562</v>
+        <v>20.588</v>
       </c>
       <c r="F39">
-        <v>37.962</v>
+        <v>38.988</v>
       </c>
       <c r="G39">
         <v>1.63</v>
@@ -4479,37 +4479,37 @@
         <v>4.34</v>
       </c>
       <c r="M39">
-        <v>7.6227696</v>
+        <v>7.8287904</v>
       </c>
       <c r="N39">
-        <v>-3.2827696</v>
+        <v>-3.4887904</v>
       </c>
       <c r="O39">
-        <v>-0.787864704</v>
+        <v>-0.8373096959999999</v>
       </c>
       <c r="P39">
-        <v>-2.494904896</v>
+        <v>-2.651480704</v>
       </c>
       <c r="Q39">
-        <v>-2.194904896</v>
+        <v>-2.351480704</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3501589177521459</v>
+        <v>0.3550679325545998</v>
       </c>
       <c r="T39">
-        <v>1.495428640792368</v>
+        <v>1.519548457579341</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1366432484067208</v>
+        <v>0.1330473734486492</v>
       </c>
       <c r="W39">
-        <v>0.1733620357199305</v>
+        <v>0.1740840874115112</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5693468683613367</v>
+        <v>0.5543640560360384</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2862940714002261</v>
+        <v>0.2878440714002262</v>
       </c>
       <c r="C40">
-        <v>50.29973285540038</v>
+        <v>48.71239092647038</v>
       </c>
       <c r="D40">
-        <v>87.65773285540038</v>
+        <v>87.09639092647038</v>
       </c>
       <c r="E40">
-        <v>20.588</v>
+        <v>21.614</v>
       </c>
       <c r="F40">
-        <v>38.988</v>
+        <v>40.014</v>
       </c>
       <c r="G40">
         <v>1.63</v>
@@ -4561,37 +4561,37 @@
         <v>4.34</v>
       </c>
       <c r="M40">
-        <v>7.8287904</v>
+        <v>8.0348112</v>
       </c>
       <c r="N40">
-        <v>-3.4887904</v>
+        <v>-3.6948112</v>
       </c>
       <c r="O40">
-        <v>-0.8373096959999999</v>
+        <v>-0.886754688</v>
       </c>
       <c r="P40">
-        <v>-2.651480704</v>
+        <v>-2.808056512</v>
       </c>
       <c r="Q40">
-        <v>-2.351480704</v>
+        <v>-2.508056512</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3550679325545998</v>
+        <v>0.3601378986620523</v>
       </c>
       <c r="T40">
-        <v>1.519548457579341</v>
+        <v>1.544459088031461</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1330473734486492</v>
+        <v>0.1296359023345813</v>
       </c>
       <c r="W40">
-        <v>0.1740840874115112</v>
+        <v>0.1747691108112161</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5543640560360384</v>
+        <v>0.5401495930607554</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2878440714002262</v>
+        <v>0.2893940714002262</v>
       </c>
       <c r="C41">
-        <v>48.71239092647038</v>
+        <v>47.13219268527335</v>
       </c>
       <c r="D41">
-        <v>87.09639092647038</v>
+        <v>86.54219268527335</v>
       </c>
       <c r="E41">
-        <v>21.614</v>
+        <v>22.64</v>
       </c>
       <c r="F41">
-        <v>40.014</v>
+        <v>41.04</v>
       </c>
       <c r="G41">
         <v>1.63</v>
@@ -4643,37 +4643,37 @@
         <v>4.34</v>
       </c>
       <c r="M41">
-        <v>8.0348112</v>
+        <v>8.240831999999999</v>
       </c>
       <c r="N41">
-        <v>-3.6948112</v>
+        <v>-3.900831999999999</v>
       </c>
       <c r="O41">
-        <v>-0.886754688</v>
+        <v>-0.9361996799999999</v>
       </c>
       <c r="P41">
-        <v>-2.808056512</v>
+        <v>-2.96463232</v>
       </c>
       <c r="Q41">
-        <v>-2.508056512</v>
+        <v>-2.66463232</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3601378986620523</v>
+        <v>0.3653768636397531</v>
       </c>
       <c r="T41">
-        <v>1.544459088031461</v>
+        <v>1.570200072831986</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1296359023345813</v>
+        <v>0.1263950047762168</v>
       </c>
       <c r="W41">
-        <v>0.1747691108112161</v>
+        <v>0.1754198830409357</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5401495930607554</v>
+        <v>0.5266458532342366</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2893940714002262</v>
+        <v>0.2909440714002262</v>
       </c>
       <c r="C42">
-        <v>47.13219268527335</v>
+        <v>45.55900262721491</v>
       </c>
       <c r="D42">
-        <v>86.54219268527335</v>
+        <v>85.99500262721492</v>
       </c>
       <c r="E42">
-        <v>22.64</v>
+        <v>23.666</v>
       </c>
       <c r="F42">
-        <v>41.04</v>
+        <v>42.066</v>
       </c>
       <c r="G42">
         <v>1.63</v>
@@ -4725,37 +4725,37 @@
         <v>4.34</v>
       </c>
       <c r="M42">
-        <v>8.240831999999999</v>
+        <v>8.4468528</v>
       </c>
       <c r="N42">
-        <v>-3.900831999999999</v>
+        <v>-4.1068528</v>
       </c>
       <c r="O42">
-        <v>-0.9361996799999999</v>
+        <v>-0.9856446720000001</v>
       </c>
       <c r="P42">
-        <v>-2.96463232</v>
+        <v>-3.121208128</v>
       </c>
       <c r="Q42">
-        <v>-2.66463232</v>
+        <v>-2.821208128</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3653768636397531</v>
+        <v>0.3707934206505964</v>
       </c>
       <c r="T42">
-        <v>1.570200072831986</v>
+        <v>1.59681363338846</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1263950047762168</v>
+        <v>0.1233121997816749</v>
       </c>
       <c r="W42">
-        <v>0.1754198830409357</v>
+        <v>0.1760389102838397</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5266458532342366</v>
+        <v>0.5138008324236454</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2909440714002262</v>
+        <v>0.2924940714002261</v>
       </c>
       <c r="C43">
-        <v>45.55900262721491</v>
+        <v>43.99268865324862</v>
       </c>
       <c r="D43">
-        <v>85.99500262721492</v>
+        <v>85.45468865324862</v>
       </c>
       <c r="E43">
-        <v>23.666</v>
+        <v>24.692</v>
       </c>
       <c r="F43">
-        <v>42.066</v>
+        <v>43.092</v>
       </c>
       <c r="G43">
         <v>1.63</v>
@@ -4807,37 +4807,37 @@
         <v>4.34</v>
       </c>
       <c r="M43">
-        <v>8.4468528</v>
+        <v>8.652873599999999</v>
       </c>
       <c r="N43">
-        <v>-4.1068528</v>
+        <v>-4.3128736</v>
       </c>
       <c r="O43">
-        <v>-0.9856446720000001</v>
+        <v>-1.035089664</v>
       </c>
       <c r="P43">
-        <v>-3.121208128</v>
+        <v>-3.277783936</v>
       </c>
       <c r="Q43">
-        <v>-2.821208128</v>
+        <v>-2.977783936</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3707934206505964</v>
+        <v>0.3763967554893998</v>
       </c>
       <c r="T43">
-        <v>1.59681363338846</v>
+        <v>1.624344902929641</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1233121997816749</v>
+        <v>0.1203761950249683</v>
       </c>
       <c r="W43">
-        <v>0.1760389102838397</v>
+        <v>0.1766284600389864</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5138008324236454</v>
+        <v>0.5015674792707014</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2924940714002262</v>
+        <v>0.3106096284447957</v>
       </c>
       <c r="C44">
-        <v>43.99268865324861</v>
+        <v>37.12075587461258</v>
       </c>
       <c r="D44">
-        <v>85.45468865324861</v>
+        <v>79.60875587461258</v>
       </c>
       <c r="E44">
-        <v>24.692</v>
+        <v>25.718</v>
       </c>
       <c r="F44">
-        <v>43.092</v>
+        <v>44.11799999999999</v>
       </c>
       <c r="G44">
         <v>1.63</v>
@@ -4889,45 +4889,45 @@
         <v>4.34</v>
       </c>
       <c r="M44">
-        <v>8.652873599999999</v>
+        <v>10.4030244</v>
       </c>
       <c r="N44">
-        <v>-4.3128736</v>
+        <v>-6.0630244</v>
       </c>
       <c r="O44">
-        <v>-1.035089664</v>
+        <v>-1.455125856</v>
       </c>
       <c r="P44">
-        <v>-3.277783936</v>
+        <v>-4.607898543999999</v>
       </c>
       <c r="Q44">
-        <v>-2.977783936</v>
+        <v>-4.307898543999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3763967554893998</v>
+        <v>0.384855570576178</v>
       </c>
       <c r="T44">
-        <v>1.624344902929641</v>
+        <v>1.665906209696528</v>
       </c>
       <c r="U44">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1203761950249683</v>
+        <v>0.10012472911243</v>
       </c>
       <c r="W44">
-        <v>0.1766284600389864</v>
+        <v>0.212190588875289</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.5015674792707014</v>
+        <v>0.4171863713017918</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.3106096284447957</v>
+        <v>0.3125096284447957</v>
       </c>
       <c r="C45">
-        <v>37.12075587461258</v>
+        <v>35.52763485598361</v>
       </c>
       <c r="D45">
-        <v>79.60875587461258</v>
+        <v>79.04163485598362</v>
       </c>
       <c r="E45">
-        <v>25.718</v>
+        <v>26.744</v>
       </c>
       <c r="F45">
-        <v>44.11799999999999</v>
+        <v>45.144</v>
       </c>
       <c r="G45">
         <v>1.63</v>
@@ -4971,37 +4971,37 @@
         <v>4.34</v>
       </c>
       <c r="M45">
-        <v>10.4030244</v>
+        <v>10.6449552</v>
       </c>
       <c r="N45">
-        <v>-6.0630244</v>
+        <v>-6.3049552</v>
       </c>
       <c r="O45">
-        <v>-1.455125856</v>
+        <v>-1.513189248</v>
       </c>
       <c r="P45">
-        <v>-4.607898543999999</v>
+        <v>-4.791765952</v>
       </c>
       <c r="Q45">
-        <v>-4.307898543999999</v>
+        <v>-4.491765952000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.384855570576178</v>
+        <v>0.3909101343364669</v>
       </c>
       <c r="T45">
-        <v>1.665906209696528</v>
+        <v>1.69565453486968</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.10012472911243</v>
+        <v>0.09784916708714753</v>
       </c>
       <c r="W45">
-        <v>0.212190588875289</v>
+        <v>0.2127271664008506</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4171863713017918</v>
+        <v>0.4077048628631147</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.3125096284447957</v>
+        <v>0.3144096284447958</v>
       </c>
       <c r="C46">
-        <v>35.52763485598361</v>
+        <v>33.94253685530552</v>
       </c>
       <c r="D46">
-        <v>79.04163485598362</v>
+        <v>78.48253685530553</v>
       </c>
       <c r="E46">
-        <v>26.744</v>
+        <v>27.77</v>
       </c>
       <c r="F46">
-        <v>45.144</v>
+        <v>46.17</v>
       </c>
       <c r="G46">
         <v>1.63</v>
@@ -5053,37 +5053,37 @@
         <v>4.34</v>
       </c>
       <c r="M46">
-        <v>10.6449552</v>
+        <v>10.886886</v>
       </c>
       <c r="N46">
-        <v>-6.3049552</v>
+        <v>-6.546886000000001</v>
       </c>
       <c r="O46">
-        <v>-1.513189248</v>
+        <v>-1.57125264</v>
       </c>
       <c r="P46">
-        <v>-4.791765952</v>
+        <v>-4.975633360000001</v>
       </c>
       <c r="Q46">
-        <v>-4.491765952000001</v>
+        <v>-4.675633360000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3909101343364669</v>
+        <v>0.3971848640516754</v>
       </c>
       <c r="T46">
-        <v>1.69565453486968</v>
+        <v>1.726484617321856</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.09784916708714753</v>
+        <v>0.09567474115187757</v>
       </c>
       <c r="W46">
-        <v>0.2127271664008506</v>
+        <v>0.2132398960363873</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4077048628631147</v>
+        <v>0.3986447547994899</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.3144096284447958</v>
+        <v>0.3163096284447958</v>
       </c>
       <c r="C47">
-        <v>33.94253685530552</v>
+        <v>32.36529281684976</v>
       </c>
       <c r="D47">
-        <v>78.48253685530553</v>
+        <v>77.93129281684976</v>
       </c>
       <c r="E47">
-        <v>27.77</v>
+        <v>28.796</v>
       </c>
       <c r="F47">
-        <v>46.17</v>
+        <v>47.196</v>
       </c>
       <c r="G47">
         <v>1.63</v>
@@ -5135,37 +5135,37 @@
         <v>4.34</v>
       </c>
       <c r="M47">
-        <v>10.886886</v>
+        <v>11.1288168</v>
       </c>
       <c r="N47">
-        <v>-6.546886000000001</v>
+        <v>-6.788816799999999</v>
       </c>
       <c r="O47">
-        <v>-1.57125264</v>
+        <v>-1.629316032</v>
       </c>
       <c r="P47">
-        <v>-4.975633360000001</v>
+        <v>-5.159500767999999</v>
       </c>
       <c r="Q47">
-        <v>-4.675633360000001</v>
+        <v>-4.859500767999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3971848640516754</v>
+        <v>0.4036919911637434</v>
       </c>
       <c r="T47">
-        <v>1.726484617321856</v>
+        <v>1.758456554679668</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.09567474115187757</v>
+        <v>0.09359485547466286</v>
       </c>
       <c r="W47">
-        <v>0.2132398960363873</v>
+        <v>0.2137303330790745</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3986447547994899</v>
+        <v>0.3899785644777619</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.3163096284447958</v>
+        <v>0.3182096284447957</v>
       </c>
       <c r="C48">
-        <v>32.36529281684976</v>
+        <v>30.79573840140066</v>
       </c>
       <c r="D48">
-        <v>77.93129281684976</v>
+        <v>77.38773840140067</v>
       </c>
       <c r="E48">
-        <v>28.796</v>
+        <v>29.822</v>
       </c>
       <c r="F48">
-        <v>47.196</v>
+        <v>48.222</v>
       </c>
       <c r="G48">
         <v>1.63</v>
@@ -5217,37 +5217,37 @@
         <v>4.34</v>
       </c>
       <c r="M48">
-        <v>11.1288168</v>
+        <v>11.3707476</v>
       </c>
       <c r="N48">
-        <v>-6.788816799999999</v>
+        <v>-7.030747600000002</v>
       </c>
       <c r="O48">
-        <v>-1.629316032</v>
+        <v>-1.687379424</v>
       </c>
       <c r="P48">
-        <v>-5.159500767999999</v>
+        <v>-5.343368176000001</v>
       </c>
       <c r="Q48">
-        <v>-4.859500767999999</v>
+        <v>-5.043368176000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.4036919911637434</v>
+        <v>0.4104446702423046</v>
       </c>
       <c r="T48">
-        <v>1.758456554679668</v>
+        <v>1.791634980239662</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.09359485547466286</v>
+        <v>0.09160347557094661</v>
       </c>
       <c r="W48">
-        <v>0.2137303330790745</v>
+        <v>0.2141999004603708</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3899785644777619</v>
+        <v>0.3816811482122776</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.3182096284447957</v>
+        <v>0.3201096284447958</v>
       </c>
       <c r="C49">
-        <v>30.79573840140066</v>
+        <v>29.23371382291141</v>
       </c>
       <c r="D49">
-        <v>77.38773840140067</v>
+        <v>76.85171382291142</v>
       </c>
       <c r="E49">
-        <v>29.822</v>
+        <v>30.84800000000001</v>
       </c>
       <c r="F49">
-        <v>48.222</v>
+        <v>49.248</v>
       </c>
       <c r="G49">
         <v>1.63</v>
@@ -5299,37 +5299,37 @@
         <v>4.34</v>
       </c>
       <c r="M49">
-        <v>11.3707476</v>
+        <v>11.6126784</v>
       </c>
       <c r="N49">
-        <v>-7.030747600000002</v>
+        <v>-7.272678400000002</v>
       </c>
       <c r="O49">
-        <v>-1.687379424</v>
+        <v>-1.745442816</v>
       </c>
       <c r="P49">
-        <v>-5.343368176000001</v>
+        <v>-5.527235584000001</v>
       </c>
       <c r="Q49">
-        <v>-5.043368176000001</v>
+        <v>-5.227235584000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.4104446702423046</v>
+        <v>0.4174570677469644</v>
       </c>
       <c r="T49">
-        <v>1.791634980239662</v>
+        <v>1.826089499090425</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.09160347557094661</v>
+        <v>0.08969506982988522</v>
       </c>
       <c r="W49">
-        <v>0.2141999004603708</v>
+        <v>0.2146499025341131</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3816811482122776</v>
+        <v>0.3737294576245218</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.3201096284447957</v>
+        <v>0.3220096284447957</v>
       </c>
       <c r="C50">
-        <v>29.23371382291143</v>
+        <v>27.67906369190157</v>
       </c>
       <c r="D50">
-        <v>76.85171382291144</v>
+        <v>76.32306369190157</v>
       </c>
       <c r="E50">
-        <v>30.848</v>
+        <v>31.874</v>
       </c>
       <c r="F50">
-        <v>49.248</v>
+        <v>50.27399999999999</v>
       </c>
       <c r="G50">
         <v>1.63</v>
@@ -5381,37 +5381,37 @@
         <v>4.34</v>
       </c>
       <c r="M50">
-        <v>11.6126784</v>
+        <v>11.8546092</v>
       </c>
       <c r="N50">
-        <v>-7.2726784</v>
+        <v>-7.514609199999999</v>
       </c>
       <c r="O50">
-        <v>-1.745442816</v>
+        <v>-1.803506208</v>
       </c>
       <c r="P50">
-        <v>-5.527235584</v>
+        <v>-5.711102991999999</v>
       </c>
       <c r="Q50">
-        <v>-5.227235584000001</v>
+        <v>-5.411102991999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.4174570677469643</v>
+        <v>0.4247444612321989</v>
       </c>
       <c r="T50">
-        <v>1.826089499090425</v>
+        <v>1.861895175543178</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08969506982988523</v>
+        <v>0.08786455820070391</v>
       </c>
       <c r="W50">
-        <v>0.2146499025341131</v>
+        <v>0.215081537176274</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3737294576245218</v>
+        <v>0.3661023258362663</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.3220096284447957</v>
+        <v>0.3239096284447958</v>
       </c>
       <c r="C51">
-        <v>27.67906369190157</v>
+        <v>26.13163686527372</v>
       </c>
       <c r="D51">
-        <v>76.32306369190157</v>
+        <v>75.80163686527372</v>
       </c>
       <c r="E51">
-        <v>31.874</v>
+        <v>32.9</v>
       </c>
       <c r="F51">
-        <v>50.27399999999999</v>
+        <v>51.3</v>
       </c>
       <c r="G51">
         <v>1.63</v>
@@ -5463,37 +5463,37 @@
         <v>4.34</v>
       </c>
       <c r="M51">
-        <v>11.8546092</v>
+        <v>12.09654</v>
       </c>
       <c r="N51">
-        <v>-7.514609199999999</v>
+        <v>-7.756539999999999</v>
       </c>
       <c r="O51">
-        <v>-1.803506208</v>
+        <v>-1.8615696</v>
       </c>
       <c r="P51">
-        <v>-5.711102991999999</v>
+        <v>-5.8949704</v>
       </c>
       <c r="Q51">
-        <v>-5.411102991999999</v>
+        <v>-5.5949704</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.4247444612321989</v>
+        <v>0.4323233504568429</v>
       </c>
       <c r="T51">
-        <v>1.861895175543178</v>
+        <v>1.899133079054042</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08786455820070391</v>
+        <v>0.08610726703668983</v>
       </c>
       <c r="W51">
-        <v>0.215081537176274</v>
+        <v>0.2154959064327485</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3661023258362663</v>
+        <v>0.3587802793195409</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.3239096284447958</v>
+        <v>0.3258096284447958</v>
       </c>
       <c r="C52">
-        <v>26.13163686527372</v>
+        <v>24.59128630224507</v>
       </c>
       <c r="D52">
-        <v>75.80163686527372</v>
+        <v>75.28728630224508</v>
       </c>
       <c r="E52">
-        <v>32.9</v>
+        <v>33.926</v>
       </c>
       <c r="F52">
-        <v>51.3</v>
+        <v>52.326</v>
       </c>
       <c r="G52">
         <v>1.63</v>
@@ -5545,37 +5545,37 @@
         <v>4.34</v>
       </c>
       <c r="M52">
-        <v>12.09654</v>
+        <v>12.3384708</v>
       </c>
       <c r="N52">
-        <v>-7.756539999999999</v>
+        <v>-7.998470800000002</v>
       </c>
       <c r="O52">
-        <v>-1.8615696</v>
+        <v>-1.919632992</v>
       </c>
       <c r="P52">
-        <v>-5.8949704</v>
+        <v>-6.078837808000001</v>
       </c>
       <c r="Q52">
-        <v>-5.5949704</v>
+        <v>-5.778837808000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.4323233504568429</v>
+        <v>0.4402115820988193</v>
       </c>
       <c r="T52">
-        <v>1.899133079054042</v>
+        <v>1.93789089699392</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08610726703668983</v>
+        <v>0.08441888925165668</v>
       </c>
       <c r="W52">
-        <v>0.2154959064327485</v>
+        <v>0.2158940259144594</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3587802793195409</v>
+        <v>0.3517453718819028</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.3258096284447958</v>
+        <v>0.3277096284447957</v>
       </c>
       <c r="C53">
-        <v>24.59128630224507</v>
+        <v>23.05786892610437</v>
       </c>
       <c r="D53">
-        <v>75.28728630224508</v>
+        <v>74.77986892610437</v>
       </c>
       <c r="E53">
-        <v>33.926</v>
+        <v>34.952</v>
       </c>
       <c r="F53">
-        <v>52.326</v>
+        <v>53.352</v>
       </c>
       <c r="G53">
         <v>1.63</v>
@@ -5627,37 +5627,37 @@
         <v>4.34</v>
       </c>
       <c r="M53">
-        <v>12.3384708</v>
+        <v>12.5804016</v>
       </c>
       <c r="N53">
-        <v>-7.998470800000002</v>
+        <v>-8.2404016</v>
       </c>
       <c r="O53">
-        <v>-1.919632992</v>
+        <v>-1.977696384</v>
       </c>
       <c r="P53">
-        <v>-6.078837808000001</v>
+        <v>-6.262705216000001</v>
       </c>
       <c r="Q53">
-        <v>-5.778837808000001</v>
+        <v>-5.962705216000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.4402115820988193</v>
+        <v>0.4484284900592114</v>
       </c>
       <c r="T53">
-        <v>1.93789089699392</v>
+        <v>1.978263624014627</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08441888925165668</v>
+        <v>0.08279544907374022</v>
       </c>
       <c r="W53">
-        <v>0.2158940259144594</v>
+        <v>0.2162768331084121</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3517453718819028</v>
+        <v>0.3449810378072509</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.3277096284447957</v>
+        <v>0.3296096284447957</v>
       </c>
       <c r="C54">
-        <v>23.05786892610437</v>
+        <v>21.53124549152191</v>
       </c>
       <c r="D54">
-        <v>74.77986892610437</v>
+        <v>74.27924549152192</v>
       </c>
       <c r="E54">
-        <v>34.952</v>
+        <v>35.978</v>
       </c>
       <c r="F54">
-        <v>53.352</v>
+        <v>54.378</v>
       </c>
       <c r="G54">
         <v>1.63</v>
@@ -5709,37 +5709,37 @@
         <v>4.34</v>
       </c>
       <c r="M54">
-        <v>12.5804016</v>
+        <v>12.8223324</v>
       </c>
       <c r="N54">
-        <v>-8.2404016</v>
+        <v>-8.482332400000001</v>
       </c>
       <c r="O54">
-        <v>-1.977696384</v>
+        <v>-2.035759776</v>
       </c>
       <c r="P54">
-        <v>-6.262705216000001</v>
+        <v>-6.446572624000001</v>
       </c>
       <c r="Q54">
-        <v>-5.962705216000001</v>
+        <v>-6.146572624000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.4484284900592114</v>
+        <v>0.4569950536774925</v>
       </c>
       <c r="T54">
-        <v>1.978263624014627</v>
+        <v>2.020354339419193</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08279544907374022</v>
+        <v>0.08123327078933003</v>
       </c>
       <c r="W54">
-        <v>0.2162768331084121</v>
+        <v>0.216645194747876</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3449810378072509</v>
+        <v>0.3384719616222084</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3296096284447957</v>
+        <v>0.3315096284447957</v>
       </c>
       <c r="C55">
-        <v>21.53124549152191</v>
+        <v>20.01128045715432</v>
       </c>
       <c r="D55">
-        <v>74.27924549152192</v>
+        <v>73.78528045715433</v>
       </c>
       <c r="E55">
-        <v>35.978</v>
+        <v>37.004</v>
       </c>
       <c r="F55">
-        <v>54.378</v>
+        <v>55.404</v>
       </c>
       <c r="G55">
         <v>1.63</v>
@@ -5791,37 +5791,37 @@
         <v>4.34</v>
       </c>
       <c r="M55">
-        <v>12.8223324</v>
+        <v>13.0642632</v>
       </c>
       <c r="N55">
-        <v>-8.482332400000001</v>
+        <v>-8.724263200000001</v>
       </c>
       <c r="O55">
-        <v>-2.035759776</v>
+        <v>-2.093823168</v>
       </c>
       <c r="P55">
-        <v>-6.446572624000001</v>
+        <v>-6.630440032000001</v>
       </c>
       <c r="Q55">
-        <v>-6.146572624000001</v>
+        <v>-6.330440032000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.4569950536774925</v>
+        <v>0.4659340765835249</v>
       </c>
       <c r="T55">
-        <v>2.020354339419193</v>
+        <v>2.064275085928306</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.08123327078933003</v>
+        <v>0.07972895095989799</v>
       </c>
       <c r="W55">
-        <v>0.216645194747876</v>
+        <v>0.2169999133636561</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3384719616222084</v>
+        <v>0.3322039623329083</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3315096284447957</v>
+        <v>0.3334096284447957</v>
       </c>
       <c r="C56">
-        <v>20.01128045715432</v>
+        <v>18.49784186329827</v>
       </c>
       <c r="D56">
-        <v>73.78528045715433</v>
+        <v>73.29784186329827</v>
       </c>
       <c r="E56">
-        <v>37.004</v>
+        <v>38.03</v>
       </c>
       <c r="F56">
-        <v>55.404</v>
+        <v>56.43</v>
       </c>
       <c r="G56">
         <v>1.63</v>
@@ -5873,37 +5873,37 @@
         <v>4.34</v>
       </c>
       <c r="M56">
-        <v>13.0642632</v>
+        <v>13.306194</v>
       </c>
       <c r="N56">
-        <v>-8.724263200000001</v>
+        <v>-8.966194</v>
       </c>
       <c r="O56">
-        <v>-2.093823168</v>
+        <v>-2.15188656</v>
       </c>
       <c r="P56">
-        <v>-6.630440032000001</v>
+        <v>-6.81430744</v>
       </c>
       <c r="Q56">
-        <v>-6.330440032000001</v>
+        <v>-6.514307440000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.4659340765835249</v>
+        <v>0.4752703893964921</v>
       </c>
       <c r="T56">
-        <v>2.064275085928306</v>
+        <v>2.110147865615602</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07972895095989799</v>
+        <v>0.07827933366971802</v>
       </c>
       <c r="W56">
-        <v>0.2169999133636561</v>
+        <v>0.2173417331206805</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3322039623329083</v>
+        <v>0.3261638902904918</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3334096284447957</v>
+        <v>0.3353096284447957</v>
       </c>
       <c r="C57">
-        <v>18.49784186329827</v>
+        <v>16.99080121436239</v>
       </c>
       <c r="D57">
-        <v>73.29784186329827</v>
+        <v>72.8168012143624</v>
       </c>
       <c r="E57">
-        <v>38.03</v>
+        <v>39.056</v>
       </c>
       <c r="F57">
-        <v>56.43</v>
+        <v>57.456</v>
       </c>
       <c r="G57">
         <v>1.63</v>
@@ -5955,37 +5955,37 @@
         <v>4.34</v>
       </c>
       <c r="M57">
-        <v>13.306194</v>
+        <v>13.5481248</v>
       </c>
       <c r="N57">
-        <v>-8.966194</v>
+        <v>-9.208124800000002</v>
       </c>
       <c r="O57">
-        <v>-2.15188656</v>
+        <v>-2.209949952000001</v>
       </c>
       <c r="P57">
-        <v>-6.81430744</v>
+        <v>-6.998174848000001</v>
       </c>
       <c r="Q57">
-        <v>-6.514307440000001</v>
+        <v>-6.698174848000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4752703893964921</v>
+        <v>0.4850310800645943</v>
       </c>
       <c r="T57">
-        <v>2.110147865615602</v>
+        <v>2.158105771652321</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07827933366971802</v>
+        <v>0.07688148842561592</v>
       </c>
       <c r="W57">
-        <v>0.2173417331206805</v>
+        <v>0.2176713450292398</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3261638902904918</v>
+        <v>0.320339535106733</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3353096284447957</v>
+        <v>0.3372096284447958</v>
       </c>
       <c r="C58">
-        <v>16.99080121436239</v>
+        <v>15.4900333659366</v>
       </c>
       <c r="D58">
-        <v>72.8168012143624</v>
+        <v>72.34203336593662</v>
       </c>
       <c r="E58">
-        <v>39.056</v>
+        <v>40.08200000000001</v>
       </c>
       <c r="F58">
-        <v>57.456</v>
+        <v>58.48200000000001</v>
       </c>
       <c r="G58">
         <v>1.63</v>
@@ -6037,37 +6037,37 @@
         <v>4.34</v>
       </c>
       <c r="M58">
-        <v>13.5481248</v>
+        <v>13.7900556</v>
       </c>
       <c r="N58">
-        <v>-9.208124800000002</v>
+        <v>-9.450055600000002</v>
       </c>
       <c r="O58">
-        <v>-2.209949952000001</v>
+        <v>-2.268013344</v>
       </c>
       <c r="P58">
-        <v>-6.998174848000001</v>
+        <v>-7.182042256000003</v>
       </c>
       <c r="Q58">
-        <v>-6.698174848000002</v>
+        <v>-6.882042256000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4850310800645943</v>
+        <v>0.4952457563451663</v>
       </c>
       <c r="T58">
-        <v>2.158105771652321</v>
+        <v>2.208294277969816</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07688148842561592</v>
+        <v>0.07553269038306124</v>
       </c>
       <c r="W58">
-        <v>0.2176713450292398</v>
+        <v>0.2179893916076742</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.320339535106733</v>
+        <v>0.3147195432627552</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3372096284447958</v>
+        <v>0.3391096284447957</v>
       </c>
       <c r="C59">
-        <v>15.4900333659366</v>
+        <v>13.99541641625081</v>
       </c>
       <c r="D59">
-        <v>72.34203336593662</v>
+        <v>71.87341641625082</v>
       </c>
       <c r="E59">
-        <v>40.08200000000001</v>
+        <v>41.108</v>
       </c>
       <c r="F59">
-        <v>58.48200000000001</v>
+        <v>59.508</v>
       </c>
       <c r="G59">
         <v>1.63</v>
@@ -6119,37 +6119,37 @@
         <v>4.34</v>
       </c>
       <c r="M59">
-        <v>13.7900556</v>
+        <v>14.0319864</v>
       </c>
       <c r="N59">
-        <v>-9.450055600000002</v>
+        <v>-9.691986400000001</v>
       </c>
       <c r="O59">
-        <v>-2.268013344</v>
+        <v>-2.326076736</v>
       </c>
       <c r="P59">
-        <v>-7.182042256000003</v>
+        <v>-7.365909664000001</v>
       </c>
       <c r="Q59">
-        <v>-6.882042256000003</v>
+        <v>-7.065909664000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4952457563451663</v>
+        <v>0.5059468457819558</v>
       </c>
       <c r="T59">
-        <v>2.208294277969816</v>
+        <v>2.260872713159574</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07553269038306124</v>
+        <v>0.07423040261783605</v>
       </c>
       <c r="W59">
-        <v>0.2179893916076742</v>
+        <v>0.2182964710627143</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3147195432627552</v>
+        <v>0.3092933442409835</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3391096284447958</v>
+        <v>0.3410096284447958</v>
       </c>
       <c r="C60">
-        <v>13.99541641625081</v>
+        <v>12.50683160182491</v>
       </c>
       <c r="D60">
-        <v>71.87341641625081</v>
+        <v>71.41083160182491</v>
       </c>
       <c r="E60">
-        <v>41.108</v>
+        <v>42.13399999999999</v>
       </c>
       <c r="F60">
-        <v>59.508</v>
+        <v>60.53399999999999</v>
       </c>
       <c r="G60">
         <v>1.63</v>
@@ -6201,37 +6201,37 @@
         <v>4.34</v>
       </c>
       <c r="M60">
-        <v>14.0319864</v>
+        <v>14.2739172</v>
       </c>
       <c r="N60">
-        <v>-9.691986399999999</v>
+        <v>-9.933917199999998</v>
       </c>
       <c r="O60">
-        <v>-2.326076736</v>
+        <v>-2.384140127999999</v>
       </c>
       <c r="P60">
-        <v>-7.365909664</v>
+        <v>-7.549777071999999</v>
       </c>
       <c r="Q60">
-        <v>-7.065909664</v>
+        <v>-7.249777071999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.5059468457819558</v>
+        <v>0.5171699395815158</v>
       </c>
       <c r="T60">
-        <v>2.260872713159573</v>
+        <v>2.316015950065905</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07423040261783606</v>
+        <v>0.0729722602005846</v>
       </c>
       <c r="W60">
-        <v>0.2182964710627143</v>
+        <v>0.2185931410447022</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3092933442409836</v>
+        <v>0.3040510841691025</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3410096284447958</v>
+        <v>0.3429096284447957</v>
       </c>
       <c r="C61">
-        <v>12.50683160182491</v>
+        <v>11.02416319712298</v>
       </c>
       <c r="D61">
-        <v>71.41083160182491</v>
+        <v>70.95416319712298</v>
       </c>
       <c r="E61">
-        <v>42.13399999999999</v>
+        <v>43.16</v>
       </c>
       <c r="F61">
-        <v>60.53399999999999</v>
+        <v>61.56</v>
       </c>
       <c r="G61">
         <v>1.63</v>
@@ -6283,37 +6283,37 @@
         <v>4.34</v>
       </c>
       <c r="M61">
-        <v>14.2739172</v>
+        <v>14.515848</v>
       </c>
       <c r="N61">
-        <v>-9.933917199999998</v>
+        <v>-10.175848</v>
       </c>
       <c r="O61">
-        <v>-2.384140127999999</v>
+        <v>-2.44220352</v>
       </c>
       <c r="P61">
-        <v>-7.549777071999999</v>
+        <v>-7.733644480000001</v>
       </c>
       <c r="Q61">
-        <v>-7.249777071999999</v>
+        <v>-7.433644480000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.5171699395815158</v>
+        <v>0.5289541880710535</v>
       </c>
       <c r="T61">
-        <v>2.316015950065905</v>
+        <v>2.373916348817552</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0729722602005846</v>
+        <v>0.07175605586390819</v>
       </c>
       <c r="W61">
-        <v>0.2185931410447022</v>
+        <v>0.2188799220272905</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3040510841691025</v>
+        <v>0.2989835660996174</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3429096284447957</v>
+        <v>0.3448096284447957</v>
       </c>
       <c r="C62">
-        <v>11.02416319712298</v>
+        <v>9.547298418033009</v>
       </c>
       <c r="D62">
-        <v>70.95416319712298</v>
+        <v>70.50329841803301</v>
       </c>
       <c r="E62">
-        <v>43.16</v>
+        <v>44.186</v>
       </c>
       <c r="F62">
-        <v>61.56</v>
+        <v>62.586</v>
       </c>
       <c r="G62">
         <v>1.63</v>
@@ -6365,37 +6365,37 @@
         <v>4.34</v>
       </c>
       <c r="M62">
-        <v>14.515848</v>
+        <v>14.7577788</v>
       </c>
       <c r="N62">
-        <v>-10.175848</v>
+        <v>-10.4177788</v>
       </c>
       <c r="O62">
-        <v>-2.44220352</v>
+        <v>-2.500266912</v>
       </c>
       <c r="P62">
-        <v>-7.733644480000001</v>
+        <v>-7.917511888</v>
       </c>
       <c r="Q62">
-        <v>-7.433644480000001</v>
+        <v>-7.617511888</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.5289541880710535</v>
+        <v>0.5413427569959525</v>
       </c>
       <c r="T62">
-        <v>2.373916348817552</v>
+        <v>2.434785998787233</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07175605586390819</v>
+        <v>0.07057972707925395</v>
       </c>
       <c r="W62">
-        <v>0.2188799220272905</v>
+        <v>0.2191573003547119</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2989835660996174</v>
+        <v>0.2940821961635581</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3448096284447957</v>
+        <v>0.3467096284447957</v>
       </c>
       <c r="C63">
-        <v>9.547298418033009</v>
+        <v>8.076127329003427</v>
       </c>
       <c r="D63">
-        <v>70.50329841803301</v>
+        <v>70.05812732900343</v>
       </c>
       <c r="E63">
-        <v>44.186</v>
+        <v>45.212</v>
       </c>
       <c r="F63">
-        <v>62.586</v>
+        <v>63.61199999999999</v>
       </c>
       <c r="G63">
         <v>1.63</v>
@@ -6447,37 +6447,37 @@
         <v>4.34</v>
       </c>
       <c r="M63">
-        <v>14.7577788</v>
+        <v>14.9997096</v>
       </c>
       <c r="N63">
-        <v>-10.4177788</v>
+        <v>-10.6597096</v>
       </c>
       <c r="O63">
-        <v>-2.500266912</v>
+        <v>-2.558330304</v>
       </c>
       <c r="P63">
-        <v>-7.917511888</v>
+        <v>-8.101379295999999</v>
       </c>
       <c r="Q63">
-        <v>-7.617511888</v>
+        <v>-7.801379295999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.5413427569959525</v>
+        <v>0.5543833558642669</v>
       </c>
       <c r="T63">
-        <v>2.434785998787233</v>
+        <v>2.498859314544791</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07057972707925395</v>
+        <v>0.06944134438442728</v>
       </c>
       <c r="W63">
-        <v>0.2191573003547119</v>
+        <v>0.2194257309941521</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2940821961635581</v>
+        <v>0.2893389349351136</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3467096284447957</v>
+        <v>0.3486096284447957</v>
       </c>
       <c r="C64">
-        <v>8.076127329003427</v>
+        <v>6.610542753675517</v>
       </c>
       <c r="D64">
-        <v>70.05812732900343</v>
+        <v>69.61854275367551</v>
       </c>
       <c r="E64">
-        <v>45.212</v>
+        <v>46.23799999999999</v>
       </c>
       <c r="F64">
-        <v>63.61199999999999</v>
+        <v>64.63799999999999</v>
       </c>
       <c r="G64">
         <v>1.63</v>
@@ -6529,37 +6529,37 @@
         <v>4.34</v>
       </c>
       <c r="M64">
-        <v>14.9997096</v>
+        <v>15.2416404</v>
       </c>
       <c r="N64">
-        <v>-10.6597096</v>
+        <v>-10.9016404</v>
       </c>
       <c r="O64">
-        <v>-2.558330304</v>
+        <v>-2.616393695999999</v>
       </c>
       <c r="P64">
-        <v>-8.101379295999999</v>
+        <v>-8.285246703999999</v>
       </c>
       <c r="Q64">
-        <v>-7.801379295999999</v>
+        <v>-7.985246703999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.5543833558642669</v>
+        <v>0.5681288519687065</v>
       </c>
       <c r="T64">
-        <v>2.498859314544791</v>
+        <v>2.566396052775732</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06944134438442728</v>
+        <v>0.06833910082276971</v>
       </c>
       <c r="W64">
-        <v>0.2194257309941521</v>
+        <v>0.2196856400259909</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2893389349351136</v>
+        <v>0.2847462534282071</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3486096284447957</v>
+        <v>0.3505096284447957</v>
       </c>
       <c r="C65">
-        <v>6.610542753675517</v>
+        <v>5.150440188859619</v>
       </c>
       <c r="D65">
-        <v>69.61854275367551</v>
+        <v>69.18444018885963</v>
       </c>
       <c r="E65">
-        <v>46.23799999999999</v>
+        <v>47.264</v>
       </c>
       <c r="F65">
-        <v>64.63799999999999</v>
+        <v>65.664</v>
       </c>
       <c r="G65">
         <v>1.63</v>
@@ -6611,37 +6611,37 @@
         <v>4.34</v>
       </c>
       <c r="M65">
-        <v>15.2416404</v>
+        <v>15.4835712</v>
       </c>
       <c r="N65">
-        <v>-10.9016404</v>
+        <v>-11.1435712</v>
       </c>
       <c r="O65">
-        <v>-2.616393695999999</v>
+        <v>-2.674457088</v>
       </c>
       <c r="P65">
-        <v>-8.285246703999999</v>
+        <v>-8.469114112000002</v>
       </c>
       <c r="Q65">
-        <v>-7.985246703999999</v>
+        <v>-8.169114112000003</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.5681288519687065</v>
+        <v>0.5826379867456151</v>
       </c>
       <c r="T65">
-        <v>2.566396052775732</v>
+        <v>2.637684832019502</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06833910082276971</v>
+        <v>0.06727130237241392</v>
       </c>
       <c r="W65">
-        <v>0.2196856400259909</v>
+        <v>0.2199374269005848</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2847462534282071</v>
+        <v>0.2802970932183914</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3505096284447957</v>
+        <v>0.3524096284447957</v>
       </c>
       <c r="C66">
-        <v>5.150440188859619</v>
+        <v>3.695717721709499</v>
       </c>
       <c r="D66">
-        <v>69.18444018885963</v>
+        <v>68.7557177217095</v>
       </c>
       <c r="E66">
-        <v>47.264</v>
+        <v>48.29</v>
       </c>
       <c r="F66">
-        <v>65.664</v>
+        <v>66.69</v>
       </c>
       <c r="G66">
         <v>1.63</v>
@@ -6693,37 +6693,37 @@
         <v>4.34</v>
       </c>
       <c r="M66">
-        <v>15.4835712</v>
+        <v>15.725502</v>
       </c>
       <c r="N66">
-        <v>-11.1435712</v>
+        <v>-11.385502</v>
       </c>
       <c r="O66">
-        <v>-2.674457088</v>
+        <v>-2.73252048</v>
       </c>
       <c r="P66">
-        <v>-8.469114112000002</v>
+        <v>-8.652981520000001</v>
       </c>
       <c r="Q66">
-        <v>-8.169114112000003</v>
+        <v>-8.35298152</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.5826379867456151</v>
+        <v>0.5979762149383471</v>
       </c>
       <c r="T66">
-        <v>2.637684832019502</v>
+        <v>2.713047255791488</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06727130237241392</v>
+        <v>0.06623635925899217</v>
       </c>
       <c r="W66">
-        <v>0.2199374269005848</v>
+        <v>0.2201814664867296</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2802970932183914</v>
+        <v>0.2759848302458007</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3524096284447957</v>
+        <v>0.3543096284447957</v>
       </c>
       <c r="C67">
-        <v>3.695717721709499</v>
+        <v>2.246275949957393</v>
       </c>
       <c r="D67">
-        <v>68.7557177217095</v>
+        <v>68.33227594995739</v>
       </c>
       <c r="E67">
-        <v>48.29</v>
+        <v>49.316</v>
       </c>
       <c r="F67">
-        <v>66.69</v>
+        <v>67.71599999999999</v>
       </c>
       <c r="G67">
         <v>1.63</v>
@@ -6775,37 +6775,37 @@
         <v>4.34</v>
       </c>
       <c r="M67">
-        <v>15.725502</v>
+        <v>15.9674328</v>
       </c>
       <c r="N67">
-        <v>-11.385502</v>
+        <v>-11.6274328</v>
       </c>
       <c r="O67">
-        <v>-2.73252048</v>
+        <v>-2.790583872</v>
       </c>
       <c r="P67">
-        <v>-8.652981520000001</v>
+        <v>-8.836848928</v>
       </c>
       <c r="Q67">
-        <v>-8.35298152</v>
+        <v>-8.536848928000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5979762149383471</v>
+        <v>0.6142166918482984</v>
       </c>
       <c r="T67">
-        <v>2.713047255791488</v>
+        <v>2.792842763314768</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06623635925899217</v>
+        <v>0.06523277805809835</v>
       </c>
       <c r="W67">
-        <v>0.2201814664867296</v>
+        <v>0.2204181109339004</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2759848302458007</v>
+        <v>0.2718032419087432</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3543096284447957</v>
+        <v>0.3562096284447958</v>
       </c>
       <c r="C68">
-        <v>2.246275949957393</v>
+        <v>0.8020179050784293</v>
       </c>
       <c r="D68">
-        <v>68.33227594995739</v>
+        <v>67.91401790507844</v>
       </c>
       <c r="E68">
-        <v>49.316</v>
+        <v>50.34200000000001</v>
       </c>
       <c r="F68">
-        <v>67.71599999999999</v>
+        <v>68.742</v>
       </c>
       <c r="G68">
         <v>1.63</v>
@@ -6857,37 +6857,37 @@
         <v>4.34</v>
       </c>
       <c r="M68">
-        <v>15.9674328</v>
+        <v>16.2093636</v>
       </c>
       <c r="N68">
-        <v>-11.6274328</v>
+        <v>-11.8693636</v>
       </c>
       <c r="O68">
-        <v>-2.790583872</v>
+        <v>-2.848647264000001</v>
       </c>
       <c r="P68">
-        <v>-8.836848928</v>
+        <v>-9.020716336000003</v>
       </c>
       <c r="Q68">
-        <v>-8.536848928000001</v>
+        <v>-8.720716336000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.6142166918482984</v>
+        <v>0.6314414400861257</v>
       </c>
       <c r="T68">
-        <v>2.792842763314768</v>
+        <v>2.877474362203094</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06523277805809835</v>
+        <v>0.06425915450499239</v>
       </c>
       <c r="W68">
-        <v>0.2204181109339004</v>
+        <v>0.2206476913677228</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2718032419087432</v>
+        <v>0.267746477104135</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3562096284447958</v>
+        <v>0.3581096284447958</v>
       </c>
       <c r="C69">
-        <v>0.8020179050784293</v>
+        <v>-0.6371510217401521</v>
       </c>
       <c r="D69">
-        <v>67.91401790507844</v>
+        <v>67.50084897825985</v>
       </c>
       <c r="E69">
-        <v>50.34200000000001</v>
+        <v>51.368</v>
       </c>
       <c r="F69">
-        <v>68.742</v>
+        <v>69.768</v>
       </c>
       <c r="G69">
         <v>1.63</v>
@@ -6939,37 +6939,37 @@
         <v>4.34</v>
       </c>
       <c r="M69">
-        <v>16.2093636</v>
+        <v>16.4512944</v>
       </c>
       <c r="N69">
-        <v>-11.8693636</v>
+        <v>-12.1112944</v>
       </c>
       <c r="O69">
-        <v>-2.848647264000001</v>
+        <v>-2.906710656</v>
       </c>
       <c r="P69">
-        <v>-9.020716336000003</v>
+        <v>-9.204583744000001</v>
       </c>
       <c r="Q69">
-        <v>-8.720716336000002</v>
+        <v>-8.904583744</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.6314414400861257</v>
+        <v>0.6497427350888171</v>
       </c>
       <c r="T69">
-        <v>2.877474362203094</v>
+        <v>2.967395436021941</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06425915450499239</v>
+        <v>0.06331416693874252</v>
       </c>
       <c r="W69">
-        <v>0.2206476913677228</v>
+        <v>0.2208705194358445</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.267746477104135</v>
+        <v>0.2638090289114271</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3581096284447958</v>
+        <v>0.3600096284447957</v>
       </c>
       <c r="C70">
-        <v>-0.6371510217401521</v>
+        <v>-2.071323150944082</v>
       </c>
       <c r="D70">
-        <v>67.50084897825985</v>
+        <v>67.09267684905592</v>
       </c>
       <c r="E70">
-        <v>51.368</v>
+        <v>52.394</v>
       </c>
       <c r="F70">
-        <v>69.768</v>
+        <v>70.794</v>
       </c>
       <c r="G70">
         <v>1.63</v>
@@ -7021,37 +7021,37 @@
         <v>4.34</v>
       </c>
       <c r="M70">
-        <v>16.4512944</v>
+        <v>16.6932252</v>
       </c>
       <c r="N70">
-        <v>-12.1112944</v>
+        <v>-12.3532252</v>
       </c>
       <c r="O70">
-        <v>-2.906710656</v>
+        <v>-2.964774048</v>
       </c>
       <c r="P70">
-        <v>-9.204583744000001</v>
+        <v>-9.388451152</v>
       </c>
       <c r="Q70">
-        <v>-8.904583744</v>
+        <v>-9.088451152000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.6497427350888171</v>
+        <v>0.6692247588013596</v>
       </c>
       <c r="T70">
-        <v>2.967395436021941</v>
+        <v>3.063117869442003</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06331416693874252</v>
+        <v>0.0623965703164419</v>
       </c>
       <c r="W70">
-        <v>0.2208705194358445</v>
+        <v>0.221086888719383</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2638090289114271</v>
+        <v>0.2599857096518413</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3600096284447957</v>
+        <v>0.3619096284447957</v>
       </c>
       <c r="C71">
-        <v>-2.071323150944082</v>
+        <v>-3.500588583383987</v>
       </c>
       <c r="D71">
-        <v>67.09267684905592</v>
+        <v>66.68941141661603</v>
       </c>
       <c r="E71">
-        <v>52.394</v>
+        <v>53.42000000000001</v>
       </c>
       <c r="F71">
-        <v>70.794</v>
+        <v>71.82000000000001</v>
       </c>
       <c r="G71">
         <v>1.63</v>
@@ -7103,37 +7103,37 @@
         <v>4.34</v>
       </c>
       <c r="M71">
-        <v>16.6932252</v>
+        <v>16.935156</v>
       </c>
       <c r="N71">
-        <v>-12.3532252</v>
+        <v>-12.595156</v>
       </c>
       <c r="O71">
-        <v>-2.964774048</v>
+        <v>-3.02283744</v>
       </c>
       <c r="P71">
-        <v>-9.388451152</v>
+        <v>-9.572318560000003</v>
       </c>
       <c r="Q71">
-        <v>-9.088451152000001</v>
+        <v>-9.272318560000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.6692247588013596</v>
+        <v>0.6900055840947382</v>
       </c>
       <c r="T71">
-        <v>3.063117869442003</v>
+        <v>3.165221798423403</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0623965703164419</v>
+        <v>0.06150519074049272</v>
       </c>
       <c r="W71">
-        <v>0.221086888719383</v>
+        <v>0.2212970760233918</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2599857096518413</v>
+        <v>0.2562716280853864</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3619096284447957</v>
+        <v>0.3638096284447957</v>
       </c>
       <c r="C72">
-        <v>-3.500588583383987</v>
+        <v>-4.925035266621961</v>
       </c>
       <c r="D72">
-        <v>66.68941141661603</v>
+        <v>66.29096473337805</v>
       </c>
       <c r="E72">
-        <v>53.42000000000001</v>
+        <v>54.44600000000001</v>
       </c>
       <c r="F72">
-        <v>71.82000000000001</v>
+        <v>72.846</v>
       </c>
       <c r="G72">
         <v>1.63</v>
@@ -7185,37 +7185,37 @@
         <v>4.34</v>
       </c>
       <c r="M72">
-        <v>16.935156</v>
+        <v>17.1770868</v>
       </c>
       <c r="N72">
-        <v>-12.595156</v>
+        <v>-12.8370868</v>
       </c>
       <c r="O72">
-        <v>-3.02283744</v>
+        <v>-3.080900832</v>
       </c>
       <c r="P72">
-        <v>-9.572318560000003</v>
+        <v>-9.756185968</v>
       </c>
       <c r="Q72">
-        <v>-9.272318560000002</v>
+        <v>-9.456185968</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.6900055840947382</v>
+        <v>0.7122195697531776</v>
       </c>
       <c r="T72">
-        <v>3.165221798423403</v>
+        <v>3.274367377679383</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06150519074049272</v>
+        <v>0.06063892044837312</v>
       </c>
       <c r="W72">
-        <v>0.2212970760233918</v>
+        <v>0.2215013425582736</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2562716280853864</v>
+        <v>0.252662168534888</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3638096284447957</v>
+        <v>0.3657096284447957</v>
       </c>
       <c r="C73">
-        <v>-4.925035266621947</v>
+        <v>-6.344749058875493</v>
       </c>
       <c r="D73">
-        <v>66.29096473337805</v>
+        <v>65.89725094112451</v>
       </c>
       <c r="E73">
-        <v>54.44599999999999</v>
+        <v>55.472</v>
       </c>
       <c r="F73">
-        <v>72.84599999999999</v>
+        <v>73.872</v>
       </c>
       <c r="G73">
         <v>1.63</v>
@@ -7267,37 +7267,37 @@
         <v>4.34</v>
       </c>
       <c r="M73">
-        <v>17.1770868</v>
+        <v>17.4190176</v>
       </c>
       <c r="N73">
-        <v>-12.8370868</v>
+        <v>-13.0790176</v>
       </c>
       <c r="O73">
-        <v>-3.080900831999999</v>
+        <v>-3.138964224</v>
       </c>
       <c r="P73">
-        <v>-9.756185967999999</v>
+        <v>-9.940053376</v>
       </c>
       <c r="Q73">
-        <v>-9.456185968</v>
+        <v>-9.640053376000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.7122195697531772</v>
+        <v>0.7360202686729337</v>
       </c>
       <c r="T73">
-        <v>3.274367377679382</v>
+        <v>3.39130906973936</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06063892044837313</v>
+        <v>0.05979671321992349</v>
       </c>
       <c r="W73">
-        <v>0.2215013425582736</v>
+        <v>0.221699935022742</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.252662168534888</v>
+        <v>0.2491529717496812</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3657096284447957</v>
+        <v>0.3676096284447957</v>
       </c>
       <c r="C74">
-        <v>-6.344749058875493</v>
+        <v>-7.759813790696015</v>
       </c>
       <c r="D74">
-        <v>65.89725094112451</v>
+        <v>65.50818620930399</v>
       </c>
       <c r="E74">
-        <v>55.472</v>
+        <v>56.498</v>
       </c>
       <c r="F74">
-        <v>73.872</v>
+        <v>74.898</v>
       </c>
       <c r="G74">
         <v>1.63</v>
@@ -7349,37 +7349,37 @@
         <v>4.34</v>
       </c>
       <c r="M74">
-        <v>17.4190176</v>
+        <v>17.6609484</v>
       </c>
       <c r="N74">
-        <v>-13.0790176</v>
+        <v>-13.3209484</v>
       </c>
       <c r="O74">
-        <v>-3.138964224</v>
+        <v>-3.197027616</v>
       </c>
       <c r="P74">
-        <v>-9.940053376</v>
+        <v>-10.123920784</v>
       </c>
       <c r="Q74">
-        <v>-9.640053376000001</v>
+        <v>-9.823920783999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.7360202686729337</v>
+        <v>0.7615839823274867</v>
       </c>
       <c r="T74">
-        <v>3.39130906973936</v>
+        <v>3.516913109359336</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05979671321992349</v>
+        <v>0.05897758016211632</v>
       </c>
       <c r="W74">
-        <v>0.221699935022742</v>
+        <v>0.221893086597773</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2491529717496812</v>
+        <v>0.2457399173421514</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3676096284447957</v>
+        <v>0.3695096284447957</v>
       </c>
       <c r="C75">
-        <v>-7.759813790696015</v>
+        <v>-9.170311324475435</v>
       </c>
       <c r="D75">
-        <v>65.50818620930399</v>
+        <v>65.12368867552456</v>
       </c>
       <c r="E75">
-        <v>56.498</v>
+        <v>57.52399999999999</v>
       </c>
       <c r="F75">
-        <v>74.898</v>
+        <v>75.92399999999999</v>
       </c>
       <c r="G75">
         <v>1.63</v>
@@ -7431,37 +7431,37 @@
         <v>4.34</v>
       </c>
       <c r="M75">
-        <v>17.6609484</v>
+        <v>17.9028792</v>
       </c>
       <c r="N75">
-        <v>-13.3209484</v>
+        <v>-13.5628792</v>
       </c>
       <c r="O75">
-        <v>-3.197027616</v>
+        <v>-3.255091008</v>
       </c>
       <c r="P75">
-        <v>-10.123920784</v>
+        <v>-10.307788192</v>
       </c>
       <c r="Q75">
-        <v>-9.823920783999998</v>
+        <v>-10.007788192</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.7615839823274867</v>
+        <v>0.7891141354939286</v>
       </c>
       <c r="T75">
-        <v>3.516913109359336</v>
+        <v>3.652178998180849</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05897758016211632</v>
+        <v>0.05818058583560124</v>
       </c>
       <c r="W75">
-        <v>0.221893086597773</v>
+        <v>0.2220810178599652</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2457399173421514</v>
+        <v>0.2424191076483385</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3695096284447957</v>
+        <v>0.3714096284447957</v>
       </c>
       <c r="C76">
-        <v>-9.170311324475435</v>
+        <v>-10.57632161186923</v>
       </c>
       <c r="D76">
-        <v>65.12368867552456</v>
+        <v>64.74367838813076</v>
       </c>
       <c r="E76">
-        <v>57.52399999999999</v>
+        <v>58.54999999999999</v>
       </c>
       <c r="F76">
-        <v>75.92399999999999</v>
+        <v>76.94999999999999</v>
       </c>
       <c r="G76">
         <v>1.63</v>
@@ -7513,37 +7513,37 @@
         <v>4.34</v>
       </c>
       <c r="M76">
-        <v>17.9028792</v>
+        <v>18.14481</v>
       </c>
       <c r="N76">
-        <v>-13.5628792</v>
+        <v>-13.80481</v>
       </c>
       <c r="O76">
-        <v>-3.255091008</v>
+        <v>-3.3131544</v>
       </c>
       <c r="P76">
-        <v>-10.307788192</v>
+        <v>-10.4916556</v>
       </c>
       <c r="Q76">
-        <v>-10.007788192</v>
+        <v>-10.1916556</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.7891141354939286</v>
+        <v>0.8188467009136858</v>
       </c>
       <c r="T76">
-        <v>3.652178998180849</v>
+        <v>3.798266158108083</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05818058583560124</v>
+        <v>0.05740484469112655</v>
       </c>
       <c r="W76">
-        <v>0.2220810178599652</v>
+        <v>0.2222639376218324</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2424191076483385</v>
+        <v>0.239186852879694</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3714096284447957</v>
+        <v>0.3733096284447958</v>
       </c>
       <c r="C77">
-        <v>-10.57632161186923</v>
+        <v>-11.97792274922081</v>
       </c>
       <c r="D77">
-        <v>64.74367838813076</v>
+        <v>64.36807725077919</v>
       </c>
       <c r="E77">
-        <v>58.54999999999999</v>
+        <v>59.576</v>
       </c>
       <c r="F77">
-        <v>76.94999999999999</v>
+        <v>77.976</v>
       </c>
       <c r="G77">
         <v>1.63</v>
@@ -7595,37 +7595,37 @@
         <v>4.34</v>
       </c>
       <c r="M77">
-        <v>18.14481</v>
+        <v>18.3867408</v>
       </c>
       <c r="N77">
-        <v>-13.80481</v>
+        <v>-14.0467408</v>
       </c>
       <c r="O77">
-        <v>-3.3131544</v>
+        <v>-3.371217792</v>
       </c>
       <c r="P77">
-        <v>-10.4916556</v>
+        <v>-10.675523008</v>
       </c>
       <c r="Q77">
-        <v>-10.1916556</v>
+        <v>-10.375523008</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.8188467009136858</v>
+        <v>0.8510569801184228</v>
       </c>
       <c r="T77">
-        <v>3.798266158108083</v>
+        <v>3.956527248029254</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05740484469112655</v>
+        <v>0.05664951778729593</v>
       </c>
       <c r="W77">
-        <v>0.2222639376218324</v>
+        <v>0.2224420437057557</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.239186852879694</v>
+        <v>0.2360396574470663</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3733096284447958</v>
+        <v>0.3752096284447957</v>
       </c>
       <c r="C78">
-        <v>-11.97792274922081</v>
+        <v>-13.37519103106754</v>
       </c>
       <c r="D78">
-        <v>64.36807725077919</v>
+        <v>63.99680896893245</v>
       </c>
       <c r="E78">
-        <v>59.576</v>
+        <v>60.602</v>
       </c>
       <c r="F78">
-        <v>77.976</v>
+        <v>79.002</v>
       </c>
       <c r="G78">
         <v>1.63</v>
@@ -7677,37 +7677,37 @@
         <v>4.34</v>
       </c>
       <c r="M78">
-        <v>18.3867408</v>
+        <v>18.6286716</v>
       </c>
       <c r="N78">
-        <v>-14.0467408</v>
+        <v>-14.2886716</v>
       </c>
       <c r="O78">
-        <v>-3.371217792</v>
+        <v>-3.429281184</v>
       </c>
       <c r="P78">
-        <v>-10.675523008</v>
+        <v>-10.859390416</v>
       </c>
       <c r="Q78">
-        <v>-10.375523008</v>
+        <v>-10.559390416</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.8510569801184228</v>
+        <v>0.8860681531670497</v>
       </c>
       <c r="T78">
-        <v>3.956527248029254</v>
+        <v>4.128550171856612</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05664951778729593</v>
+        <v>0.0559138097640843</v>
       </c>
       <c r="W78">
-        <v>0.2224420437057557</v>
+        <v>0.2226155236576289</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2360396574470663</v>
+        <v>0.2329742073503512</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3752096284447957</v>
+        <v>0.3771096284447958</v>
       </c>
       <c r="C79">
-        <v>-13.37519103106754</v>
+        <v>-14.76820100180625</v>
       </c>
       <c r="D79">
-        <v>63.99680896893245</v>
+        <v>63.62979899819374</v>
       </c>
       <c r="E79">
-        <v>60.602</v>
+        <v>61.62799999999999</v>
       </c>
       <c r="F79">
-        <v>79.002</v>
+        <v>80.02799999999999</v>
       </c>
       <c r="G79">
         <v>1.63</v>
@@ -7759,37 +7759,37 @@
         <v>4.34</v>
       </c>
       <c r="M79">
-        <v>18.6286716</v>
+        <v>18.8706024</v>
       </c>
       <c r="N79">
-        <v>-14.2886716</v>
+        <v>-14.5306024</v>
       </c>
       <c r="O79">
-        <v>-3.429281184</v>
+        <v>-3.487344576</v>
       </c>
       <c r="P79">
-        <v>-10.859390416</v>
+        <v>-11.043257824</v>
       </c>
       <c r="Q79">
-        <v>-10.559390416</v>
+        <v>-10.743257824</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.8860681531670497</v>
+        <v>0.9242621601291886</v>
       </c>
       <c r="T79">
-        <v>4.128550171856612</v>
+        <v>4.316211543304641</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0559138097640843</v>
+        <v>0.05519696604916015</v>
       </c>
       <c r="W79">
-        <v>0.2226155236576289</v>
+        <v>0.222784555405608</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2329742073503512</v>
+        <v>0.2299873585381673</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3771096284447958</v>
+        <v>0.3790096284447957</v>
       </c>
       <c r="C80">
-        <v>-14.76820100180625</v>
+        <v>-16.15702550559034</v>
       </c>
       <c r="D80">
-        <v>63.62979899819374</v>
+        <v>63.26697449440966</v>
       </c>
       <c r="E80">
-        <v>61.62799999999999</v>
+        <v>62.654</v>
       </c>
       <c r="F80">
-        <v>80.02799999999999</v>
+        <v>81.054</v>
       </c>
       <c r="G80">
         <v>1.63</v>
@@ -7841,37 +7841,37 @@
         <v>4.34</v>
       </c>
       <c r="M80">
-        <v>18.8706024</v>
+        <v>19.1125332</v>
       </c>
       <c r="N80">
-        <v>-14.5306024</v>
+        <v>-14.7725332</v>
       </c>
       <c r="O80">
-        <v>-3.487344576</v>
+        <v>-3.545407968</v>
       </c>
       <c r="P80">
-        <v>-11.043257824</v>
+        <v>-11.227125232</v>
       </c>
       <c r="Q80">
-        <v>-10.743257824</v>
+        <v>-10.927125232</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.9242621601291886</v>
+        <v>0.9660936915639117</v>
       </c>
       <c r="T80">
-        <v>4.316211543304641</v>
+        <v>4.521745426319147</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05519696604916015</v>
+        <v>0.05449827027638596</v>
       </c>
       <c r="W80">
-        <v>0.222784555405608</v>
+        <v>0.2229493078688282</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2299873585381673</v>
+        <v>0.2270761261516082</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3790096284447957</v>
+        <v>0.3809096284447957</v>
       </c>
       <c r="C81">
-        <v>-16.15702550559034</v>
+        <v>-17.54173573453019</v>
       </c>
       <c r="D81">
-        <v>63.26697449440966</v>
+        <v>62.90826426546981</v>
       </c>
       <c r="E81">
-        <v>62.654</v>
+        <v>63.68</v>
       </c>
       <c r="F81">
-        <v>81.054</v>
+        <v>82.08</v>
       </c>
       <c r="G81">
         <v>1.63</v>
@@ -7923,37 +7923,37 @@
         <v>4.34</v>
       </c>
       <c r="M81">
-        <v>19.1125332</v>
+        <v>19.354464</v>
       </c>
       <c r="N81">
-        <v>-14.7725332</v>
+        <v>-15.014464</v>
       </c>
       <c r="O81">
-        <v>-3.545407968</v>
+        <v>-3.60347136</v>
       </c>
       <c r="P81">
-        <v>-11.227125232</v>
+        <v>-11.41099264</v>
       </c>
       <c r="Q81">
-        <v>-10.927125232</v>
+        <v>-11.11099264</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.9660936915639117</v>
+        <v>1.012108376142107</v>
       </c>
       <c r="T81">
-        <v>4.521745426319147</v>
+        <v>4.747832697635105</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05449827027638596</v>
+        <v>0.05381704189793114</v>
       </c>
       <c r="W81">
-        <v>0.2229493078688282</v>
+        <v>0.2231099415204678</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2270761261516082</v>
+        <v>0.2242376745747131</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3809096284447957</v>
+        <v>0.3828096284447958</v>
       </c>
       <c r="C82">
-        <v>-17.54173573453019</v>
+        <v>-18.92240127526259</v>
       </c>
       <c r="D82">
-        <v>62.90826426546981</v>
+        <v>62.55359872473741</v>
       </c>
       <c r="E82">
-        <v>63.68</v>
+        <v>64.70599999999999</v>
       </c>
       <c r="F82">
-        <v>82.08</v>
+        <v>83.10599999999999</v>
       </c>
       <c r="G82">
         <v>1.63</v>
@@ -8005,37 +8005,37 @@
         <v>4.34</v>
       </c>
       <c r="M82">
-        <v>19.354464</v>
+        <v>19.5963948</v>
       </c>
       <c r="N82">
-        <v>-15.014464</v>
+        <v>-15.2563948</v>
       </c>
       <c r="O82">
-        <v>-3.60347136</v>
+        <v>-3.661534752</v>
       </c>
       <c r="P82">
-        <v>-11.41099264</v>
+        <v>-11.594860048</v>
       </c>
       <c r="Q82">
-        <v>-11.11099264</v>
+        <v>-11.294860048</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>1.012108376142107</v>
+        <v>1.062966711728534</v>
       </c>
       <c r="T82">
-        <v>4.747832697635105</v>
+        <v>4.997718629089585</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05381704189793114</v>
+        <v>0.05315263397326533</v>
       </c>
       <c r="W82">
-        <v>0.2231099415204678</v>
+        <v>0.223266608909104</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2242376745747131</v>
+        <v>0.2214693082219389</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3828096284447958</v>
+        <v>0.3847096284447957</v>
       </c>
       <c r="C83">
-        <v>-18.92240127526259</v>
+        <v>-20.29909015395391</v>
       </c>
       <c r="D83">
-        <v>62.55359872473741</v>
+        <v>62.2029098460461</v>
       </c>
       <c r="E83">
-        <v>64.70599999999999</v>
+        <v>65.732</v>
       </c>
       <c r="F83">
-        <v>83.10599999999999</v>
+        <v>84.13200000000001</v>
       </c>
       <c r="G83">
         <v>1.63</v>
@@ -8087,37 +8087,37 @@
         <v>4.34</v>
       </c>
       <c r="M83">
-        <v>19.5963948</v>
+        <v>19.8383256</v>
       </c>
       <c r="N83">
-        <v>-15.2563948</v>
+        <v>-15.4983256</v>
       </c>
       <c r="O83">
-        <v>-3.661534752</v>
+        <v>-3.719598144</v>
       </c>
       <c r="P83">
-        <v>-11.594860048</v>
+        <v>-11.778727456</v>
       </c>
       <c r="Q83">
-        <v>-11.294860048</v>
+        <v>-11.478727456</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>1.062966711728534</v>
+        <v>1.119475973491231</v>
       </c>
       <c r="T83">
-        <v>4.997718629089585</v>
+        <v>5.275369664039006</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05315263397326533</v>
+        <v>0.05250443111993282</v>
       </c>
       <c r="W83">
-        <v>0.223266608909104</v>
+        <v>0.2234194551419199</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2214693082219389</v>
+        <v>0.2187684629997201</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3847096284447957</v>
+        <v>0.3866096284447957</v>
       </c>
       <c r="C84">
-        <v>-20.29909015395391</v>
+        <v>-21.67186887979801</v>
       </c>
       <c r="D84">
-        <v>62.2029098460461</v>
+        <v>61.85613112020199</v>
       </c>
       <c r="E84">
-        <v>65.732</v>
+        <v>66.75800000000001</v>
       </c>
       <c r="F84">
-        <v>84.13200000000001</v>
+        <v>85.158</v>
       </c>
       <c r="G84">
         <v>1.63</v>
@@ -8169,37 +8169,37 @@
         <v>4.34</v>
       </c>
       <c r="M84">
-        <v>19.8383256</v>
+        <v>20.0802564</v>
       </c>
       <c r="N84">
-        <v>-15.4983256</v>
+        <v>-15.7402564</v>
       </c>
       <c r="O84">
-        <v>-3.719598144</v>
+        <v>-3.777661536</v>
       </c>
       <c r="P84">
-        <v>-11.778727456</v>
+        <v>-11.962594864</v>
       </c>
       <c r="Q84">
-        <v>-11.478727456</v>
+        <v>-11.662594864</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.119475973491231</v>
+        <v>1.182633383696597</v>
       </c>
       <c r="T84">
-        <v>5.275369664039006</v>
+        <v>5.585685526629537</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05250443111993282</v>
+        <v>0.05187184761246375</v>
       </c>
       <c r="W84">
-        <v>0.2234194551419199</v>
+        <v>0.2235686183329811</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2187684629997201</v>
+        <v>0.2161326983852656</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3866096284447957</v>
+        <v>0.3885096284447958</v>
       </c>
       <c r="C85">
-        <v>-21.67186887979801</v>
+        <v>-23.04080248706698</v>
       </c>
       <c r="D85">
-        <v>61.85613112020199</v>
+        <v>61.51319751293301</v>
       </c>
       <c r="E85">
-        <v>66.75800000000001</v>
+        <v>67.78399999999999</v>
       </c>
       <c r="F85">
-        <v>85.158</v>
+        <v>86.184</v>
       </c>
       <c r="G85">
         <v>1.63</v>
@@ -8251,37 +8251,37 @@
         <v>4.34</v>
       </c>
       <c r="M85">
-        <v>20.0802564</v>
+        <v>20.3221872</v>
       </c>
       <c r="N85">
-        <v>-15.7402564</v>
+        <v>-15.9821872</v>
       </c>
       <c r="O85">
-        <v>-3.777661536</v>
+        <v>-3.835724928</v>
       </c>
       <c r="P85">
-        <v>-11.962594864</v>
+        <v>-12.146462272</v>
       </c>
       <c r="Q85">
-        <v>-11.662594864</v>
+        <v>-11.846462272</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.182633383696597</v>
+        <v>1.253685470177635</v>
       </c>
       <c r="T85">
-        <v>5.585685526629537</v>
+        <v>5.934790872043884</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05187184761246375</v>
+        <v>0.05125432561707727</v>
       </c>
       <c r="W85">
-        <v>0.2235686183329811</v>
+        <v>0.2237142300194932</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2161326983852656</v>
+        <v>0.2135596900711553</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3885096284447958</v>
+        <v>0.3904096284447957</v>
       </c>
       <c r="C86">
-        <v>-23.04080248706698</v>
+        <v>-24.40595457577101</v>
       </c>
       <c r="D86">
-        <v>61.51319751293301</v>
+        <v>61.17404542422899</v>
       </c>
       <c r="E86">
-        <v>67.78399999999999</v>
+        <v>68.81</v>
       </c>
       <c r="F86">
-        <v>86.184</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="G86">
         <v>1.63</v>
@@ -8333,37 +8333,37 @@
         <v>4.34</v>
       </c>
       <c r="M86">
-        <v>20.3221872</v>
+        <v>20.564118</v>
       </c>
       <c r="N86">
-        <v>-15.9821872</v>
+        <v>-16.224118</v>
       </c>
       <c r="O86">
-        <v>-3.835724928</v>
+        <v>-3.89378832</v>
       </c>
       <c r="P86">
-        <v>-12.146462272</v>
+        <v>-12.33032968</v>
       </c>
       <c r="Q86">
-        <v>-11.846462272</v>
+        <v>-12.03032968</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.253685470177634</v>
+        <v>1.334211168189476</v>
       </c>
       <c r="T86">
-        <v>5.934790872043879</v>
+        <v>6.330443596846805</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05125432561707727</v>
+        <v>0.05065133355099401</v>
       </c>
       <c r="W86">
-        <v>0.2237142300194932</v>
+        <v>0.2238564155486756</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2135596900711553</v>
+        <v>0.2110472231291417</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3904096284447957</v>
+        <v>0.3923096284447958</v>
       </c>
       <c r="C87">
-        <v>-24.40595457577101</v>
+        <v>-25.76738735098046</v>
       </c>
       <c r="D87">
-        <v>61.17404542422899</v>
+        <v>60.83861264901952</v>
       </c>
       <c r="E87">
-        <v>68.81</v>
+        <v>69.83599999999998</v>
       </c>
       <c r="F87">
-        <v>87.20999999999999</v>
+        <v>88.23599999999999</v>
       </c>
       <c r="G87">
         <v>1.63</v>
@@ -8415,37 +8415,37 @@
         <v>4.34</v>
       </c>
       <c r="M87">
-        <v>20.564118</v>
+        <v>20.8060488</v>
       </c>
       <c r="N87">
-        <v>-16.224118</v>
+        <v>-16.4660488</v>
       </c>
       <c r="O87">
-        <v>-3.89378832</v>
+        <v>-3.951851712</v>
       </c>
       <c r="P87">
-        <v>-12.33032968</v>
+        <v>-12.514197088</v>
       </c>
       <c r="Q87">
-        <v>-12.03032968</v>
+        <v>-12.214197088</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.334211168189476</v>
+        <v>1.426240537345868</v>
       </c>
       <c r="T87">
-        <v>6.330443596846805</v>
+        <v>6.782618139478719</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05065133355099401</v>
+        <v>0.05006236455621502</v>
       </c>
       <c r="W87">
-        <v>0.2238564155486756</v>
+        <v>0.2239952944376445</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2110472231291417</v>
+        <v>0.2085931856508959</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3923096284447958</v>
+        <v>0.3942096284447957</v>
       </c>
       <c r="C88">
-        <v>-25.76738735098046</v>
+        <v>-27.12516166086137</v>
       </c>
       <c r="D88">
-        <v>60.83861264901952</v>
+        <v>60.50683833913862</v>
       </c>
       <c r="E88">
-        <v>69.83599999999998</v>
+        <v>70.86199999999999</v>
       </c>
       <c r="F88">
-        <v>88.23599999999999</v>
+        <v>89.262</v>
       </c>
       <c r="G88">
         <v>1.63</v>
@@ -8497,37 +8497,37 @@
         <v>4.34</v>
       </c>
       <c r="M88">
-        <v>20.8060488</v>
+        <v>21.0479796</v>
       </c>
       <c r="N88">
-        <v>-16.4660488</v>
+        <v>-16.7079796</v>
       </c>
       <c r="O88">
-        <v>-3.951851712</v>
+        <v>-4.009915104</v>
       </c>
       <c r="P88">
-        <v>-12.514197088</v>
+        <v>-12.698064496</v>
       </c>
       <c r="Q88">
-        <v>-12.214197088</v>
+        <v>-12.398064496</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.426240537345868</v>
+        <v>1.532428270987857</v>
       </c>
       <c r="T88">
-        <v>6.782618139478719</v>
+        <v>7.304357996361698</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05006236455621502</v>
+        <v>0.04948693507855737</v>
       </c>
       <c r="W88">
-        <v>0.2239952944376445</v>
+        <v>0.2241309807084762</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2085931856508959</v>
+        <v>0.2061955628273223</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3942096284447957</v>
+        <v>0.3961096284447957</v>
       </c>
       <c r="C89">
-        <v>-27.12516166086137</v>
+        <v>-28.47933703347314</v>
       </c>
       <c r="D89">
-        <v>60.50683833913862</v>
+        <v>60.17866296652685</v>
       </c>
       <c r="E89">
-        <v>70.86199999999999</v>
+        <v>71.88800000000001</v>
       </c>
       <c r="F89">
-        <v>89.262</v>
+        <v>90.288</v>
       </c>
       <c r="G89">
         <v>1.63</v>
@@ -8579,37 +8579,37 @@
         <v>4.34</v>
       </c>
       <c r="M89">
-        <v>21.0479796</v>
+        <v>21.2899104</v>
       </c>
       <c r="N89">
-        <v>-16.7079796</v>
+        <v>-16.9499104</v>
       </c>
       <c r="O89">
-        <v>-4.009915104</v>
+        <v>-4.067978496</v>
       </c>
       <c r="P89">
-        <v>-12.698064496</v>
+        <v>-12.881931904</v>
       </c>
       <c r="Q89">
-        <v>-12.398064496</v>
+        <v>-12.581931904</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.532428270987857</v>
+        <v>1.656313960236846</v>
       </c>
       <c r="T89">
-        <v>7.304357996361698</v>
+        <v>7.913054496058507</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04948693507855737</v>
+        <v>0.04892458354357376</v>
       </c>
       <c r="W89">
-        <v>0.2241309807084762</v>
+        <v>0.2242635832004253</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2061955628273223</v>
+        <v>0.2038524314315574</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3961096284447957</v>
+        <v>0.3980096284447958</v>
       </c>
       <c r="C90">
-        <v>-28.47933703347314</v>
+        <v>-29.82997171237525</v>
       </c>
       <c r="D90">
-        <v>60.17866296652685</v>
+        <v>59.85402828762474</v>
       </c>
       <c r="E90">
-        <v>71.88800000000001</v>
+        <v>72.91399999999999</v>
       </c>
       <c r="F90">
-        <v>90.288</v>
+        <v>91.31399999999999</v>
       </c>
       <c r="G90">
         <v>1.63</v>
@@ -8661,37 +8661,37 @@
         <v>4.34</v>
       </c>
       <c r="M90">
-        <v>21.2899104</v>
+        <v>21.5318412</v>
       </c>
       <c r="N90">
-        <v>-16.9499104</v>
+        <v>-17.1918412</v>
       </c>
       <c r="O90">
-        <v>-4.067978496</v>
+        <v>-4.126041888</v>
       </c>
       <c r="P90">
-        <v>-12.881931904</v>
+        <v>-13.065799312</v>
       </c>
       <c r="Q90">
-        <v>-12.581931904</v>
+        <v>-12.765799312</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.656313960236846</v>
+        <v>1.802724320258377</v>
       </c>
       <c r="T90">
-        <v>7.913054496058507</v>
+        <v>8.632423086609283</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04892458354357376</v>
+        <v>0.04837486912173586</v>
       </c>
       <c r="W90">
-        <v>0.2242635832004253</v>
+        <v>0.2243932058610947</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2038524314315574</v>
+        <v>0.2015619546738994</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3980096284447958</v>
+        <v>0.3999096284447957</v>
       </c>
       <c r="C91">
-        <v>-29.82997171237525</v>
+        <v>-31.17712269108753</v>
       </c>
       <c r="D91">
-        <v>59.85402828762474</v>
+        <v>59.53287730891248</v>
       </c>
       <c r="E91">
-        <v>72.91399999999999</v>
+        <v>73.94</v>
       </c>
       <c r="F91">
-        <v>91.31399999999999</v>
+        <v>92.34</v>
       </c>
       <c r="G91">
         <v>1.63</v>
@@ -8743,37 +8743,37 @@
         <v>4.34</v>
       </c>
       <c r="M91">
-        <v>21.5318412</v>
+        <v>21.773772</v>
       </c>
       <c r="N91">
-        <v>-17.1918412</v>
+        <v>-17.433772</v>
       </c>
       <c r="O91">
-        <v>-4.126041888</v>
+        <v>-4.18410528</v>
       </c>
       <c r="P91">
-        <v>-13.065799312</v>
+        <v>-13.24966672</v>
       </c>
       <c r="Q91">
-        <v>-12.765799312</v>
+        <v>-12.94966672</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.802724320258377</v>
+        <v>1.978416752284215</v>
       </c>
       <c r="T91">
-        <v>8.632423086609283</v>
+        <v>9.49566539527021</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04837486912173586</v>
+        <v>0.04783737057593879</v>
       </c>
       <c r="W91">
-        <v>0.2243932058610947</v>
+        <v>0.2245199480181937</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2015619546738994</v>
+        <v>0.199322377399745</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3999096284447957</v>
+        <v>0.4018096284447957</v>
       </c>
       <c r="C92">
-        <v>-31.17712269108753</v>
+        <v>-32.52084574644716</v>
       </c>
       <c r="D92">
-        <v>59.53287730891248</v>
+        <v>59.21515425355283</v>
       </c>
       <c r="E92">
-        <v>73.94</v>
+        <v>74.96600000000001</v>
       </c>
       <c r="F92">
-        <v>92.34</v>
+        <v>93.366</v>
       </c>
       <c r="G92">
         <v>1.63</v>
@@ -8825,37 +8825,37 @@
         <v>4.34</v>
       </c>
       <c r="M92">
-        <v>21.773772</v>
+        <v>22.0157028</v>
       </c>
       <c r="N92">
-        <v>-17.433772</v>
+        <v>-17.6757028</v>
       </c>
       <c r="O92">
-        <v>-4.18410528</v>
+        <v>-4.242168672</v>
       </c>
       <c r="P92">
-        <v>-13.24966672</v>
+        <v>-13.433534128</v>
       </c>
       <c r="Q92">
-        <v>-12.94966672</v>
+        <v>-13.133534128</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.978416752284215</v>
+        <v>2.193151946982461</v>
       </c>
       <c r="T92">
-        <v>9.49566539527021</v>
+        <v>10.55073932807801</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04783737057593879</v>
+        <v>0.04731168518499441</v>
       </c>
       <c r="W92">
-        <v>0.2245199480181937</v>
+        <v>0.2246439046333783</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.199322377399745</v>
+        <v>0.1971320216041433</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.4018096284447957</v>
+        <v>0.4037096284447957</v>
       </c>
       <c r="C93">
-        <v>-32.52084574644716</v>
+        <v>-33.86119547090312</v>
       </c>
       <c r="D93">
-        <v>59.21515425355283</v>
+        <v>58.90080452909687</v>
       </c>
       <c r="E93">
-        <v>74.96600000000001</v>
+        <v>75.99199999999999</v>
       </c>
       <c r="F93">
-        <v>93.366</v>
+        <v>94.392</v>
       </c>
       <c r="G93">
         <v>1.63</v>
@@ -8907,37 +8907,37 @@
         <v>4.34</v>
       </c>
       <c r="M93">
-        <v>22.0157028</v>
+        <v>22.2576336</v>
       </c>
       <c r="N93">
-        <v>-17.6757028</v>
+        <v>-17.9176336</v>
       </c>
       <c r="O93">
-        <v>-4.242168672</v>
+        <v>-4.300232063999999</v>
       </c>
       <c r="P93">
-        <v>-13.433534128</v>
+        <v>-13.617401536</v>
       </c>
       <c r="Q93">
-        <v>-13.133534128</v>
+        <v>-13.317401536</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>2.193151946982461</v>
+        <v>2.461570940355269</v>
       </c>
       <c r="T93">
-        <v>10.55073932807801</v>
+        <v>11.86958174408777</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04731168518499441</v>
+        <v>0.04679742773733143</v>
       </c>
       <c r="W93">
-        <v>0.2246439046333783</v>
+        <v>0.2247651665395373</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1971320216041433</v>
+        <v>0.194989282238881</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.4037096284447957</v>
+        <v>0.4056096284447958</v>
       </c>
       <c r="C94">
-        <v>-33.86119547090312</v>
+        <v>-35.19822530378725</v>
       </c>
       <c r="D94">
-        <v>58.90080452909687</v>
+        <v>58.58977469621275</v>
       </c>
       <c r="E94">
-        <v>75.99199999999999</v>
+        <v>77.018</v>
       </c>
       <c r="F94">
-        <v>94.392</v>
+        <v>95.41800000000001</v>
       </c>
       <c r="G94">
         <v>1.63</v>
@@ -8989,37 +8989,37 @@
         <v>4.34</v>
       </c>
       <c r="M94">
-        <v>22.2576336</v>
+        <v>22.4995644</v>
       </c>
       <c r="N94">
-        <v>-17.9176336</v>
+        <v>-18.1595644</v>
       </c>
       <c r="O94">
-        <v>-4.300232063999999</v>
+        <v>-4.358295456</v>
       </c>
       <c r="P94">
-        <v>-13.617401536</v>
+        <v>-13.801268944</v>
       </c>
       <c r="Q94">
-        <v>-13.317401536</v>
+        <v>-13.501268944</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.461570940355269</v>
+        <v>2.806681074691737</v>
       </c>
       <c r="T94">
-        <v>11.86958174408777</v>
+        <v>13.56523627895745</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04679742773733143</v>
+        <v>0.04629422958961818</v>
       </c>
       <c r="W94">
-        <v>0.2247651665395373</v>
+        <v>0.224883820662768</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.194989282238881</v>
+        <v>0.1928926232900757</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.4056096284447958</v>
+        <v>0.4075096284447957</v>
       </c>
       <c r="C95">
-        <v>-35.19822530378725</v>
+        <v>-36.53198756160005</v>
       </c>
       <c r="D95">
-        <v>58.58977469621275</v>
+        <v>58.28201243839995</v>
       </c>
       <c r="E95">
-        <v>77.018</v>
+        <v>78.04400000000001</v>
       </c>
       <c r="F95">
-        <v>95.41800000000001</v>
+        <v>96.444</v>
       </c>
       <c r="G95">
         <v>1.63</v>
@@ -9071,37 +9071,37 @@
         <v>4.34</v>
       </c>
       <c r="M95">
-        <v>22.4995644</v>
+        <v>22.7414952</v>
       </c>
       <c r="N95">
-        <v>-18.1595644</v>
+        <v>-18.4014952</v>
       </c>
       <c r="O95">
-        <v>-4.358295456</v>
+        <v>-4.416358848000001</v>
       </c>
       <c r="P95">
-        <v>-13.801268944</v>
+        <v>-13.985136352</v>
       </c>
       <c r="Q95">
-        <v>-13.501268944</v>
+        <v>-13.685136352</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.806681074691737</v>
+        <v>3.266827920473693</v>
       </c>
       <c r="T95">
-        <v>13.56523627895745</v>
+        <v>15.82610899211703</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04629422958961818</v>
+        <v>0.04580173778547331</v>
       </c>
       <c r="W95">
-        <v>0.224883820662768</v>
+        <v>0.2249999502301854</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1928926232900757</v>
+        <v>0.1908405741061387</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.4075096284447957</v>
+        <v>0.4094096284447957</v>
       </c>
       <c r="C96">
-        <v>-36.53198756160005</v>
+        <v>-37.8625334673468</v>
       </c>
       <c r="D96">
-        <v>58.28201243839995</v>
+        <v>57.9774665326532</v>
       </c>
       <c r="E96">
-        <v>78.04400000000001</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="F96">
-        <v>96.444</v>
+        <v>97.47</v>
       </c>
       <c r="G96">
         <v>1.63</v>
@@ -9153,37 +9153,37 @@
         <v>4.34</v>
       </c>
       <c r="M96">
-        <v>22.7414952</v>
+        <v>22.983426</v>
       </c>
       <c r="N96">
-        <v>-18.4014952</v>
+        <v>-18.643426</v>
       </c>
       <c r="O96">
-        <v>-4.416358848000001</v>
+        <v>-4.47442224</v>
       </c>
       <c r="P96">
-        <v>-13.985136352</v>
+        <v>-14.16900376</v>
       </c>
       <c r="Q96">
-        <v>-13.685136352</v>
+        <v>-13.86900376</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>3.266827920473693</v>
+        <v>3.911033504568434</v>
       </c>
       <c r="T96">
-        <v>15.82610899211703</v>
+        <v>18.99133079054044</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04580173778547331</v>
+        <v>0.04531961422983675</v>
       </c>
       <c r="W96">
-        <v>0.2249999502301854</v>
+        <v>0.2251136349646045</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1908405741061387</v>
+        <v>0.1888317259576531</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.4094096284447957</v>
+        <v>0.4113096284447957</v>
       </c>
       <c r="C97">
-        <v>-37.8625334673468</v>
+        <v>-39.18991317895864</v>
       </c>
       <c r="D97">
-        <v>57.9774665326532</v>
+        <v>57.67608682104137</v>
       </c>
       <c r="E97">
-        <v>79.06999999999999</v>
+        <v>80.096</v>
       </c>
       <c r="F97">
-        <v>97.47</v>
+        <v>98.49600000000001</v>
       </c>
       <c r="G97">
         <v>1.63</v>
@@ -9235,37 +9235,37 @@
         <v>4.34</v>
       </c>
       <c r="M97">
-        <v>22.983426</v>
+        <v>23.2253568</v>
       </c>
       <c r="N97">
-        <v>-18.643426</v>
+        <v>-18.8853568</v>
       </c>
       <c r="O97">
-        <v>-4.47442224</v>
+        <v>-4.532485632000001</v>
       </c>
       <c r="P97">
-        <v>-14.16900376</v>
+        <v>-14.352871168</v>
       </c>
       <c r="Q97">
-        <v>-13.86900376</v>
+        <v>-14.052871168</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.911033504568434</v>
+        <v>4.877341880710545</v>
       </c>
       <c r="T97">
-        <v>18.99133079054044</v>
+        <v>23.73916348817556</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04531961422983675</v>
+        <v>0.04484753491494261</v>
       </c>
       <c r="W97">
-        <v>0.2251136349646045</v>
+        <v>0.2252249512670565</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1888317259576531</v>
+        <v>0.1868647288122609</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.4113096284447957</v>
+        <v>0.4132096284447957</v>
       </c>
       <c r="C98">
-        <v>-39.18991317895863</v>
+        <v>-40.51417581683188</v>
       </c>
       <c r="D98">
-        <v>57.67608682104137</v>
+        <v>57.37782418316811</v>
       </c>
       <c r="E98">
-        <v>80.096</v>
+        <v>81.12199999999999</v>
       </c>
       <c r="F98">
-        <v>98.496</v>
+        <v>99.52199999999999</v>
       </c>
       <c r="G98">
         <v>1.63</v>
@@ -9317,37 +9317,37 @@
         <v>4.34</v>
       </c>
       <c r="M98">
-        <v>23.2253568</v>
+        <v>23.4672876</v>
       </c>
       <c r="N98">
-        <v>-18.8853568</v>
+        <v>-19.1272876</v>
       </c>
       <c r="O98">
-        <v>-4.532485632</v>
+        <v>-4.590549024</v>
       </c>
       <c r="P98">
-        <v>-14.352871168</v>
+        <v>-14.536738576</v>
       </c>
       <c r="Q98">
-        <v>-14.052871168</v>
+        <v>-14.236738576</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.877341880710532</v>
+        <v>6.487855840947376</v>
       </c>
       <c r="T98">
-        <v>23.7391634881755</v>
+        <v>31.652217984234</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04484753491494262</v>
+        <v>0.04438518919417002</v>
       </c>
       <c r="W98">
-        <v>0.2252249512670565</v>
+        <v>0.2253339723880147</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1868647288122609</v>
+        <v>0.1849382883090417</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.4132096284447957</v>
+        <v>0.4151096284447957</v>
       </c>
       <c r="C99">
-        <v>-40.51417581683188</v>
+        <v>-41.8353694905173</v>
       </c>
       <c r="D99">
-        <v>57.37782418316811</v>
+        <v>57.08263050948268</v>
       </c>
       <c r="E99">
-        <v>81.12199999999999</v>
+        <v>82.148</v>
       </c>
       <c r="F99">
-        <v>99.52199999999999</v>
+        <v>100.548</v>
       </c>
       <c r="G99">
         <v>1.63</v>
@@ -9399,37 +9399,37 @@
         <v>4.34</v>
       </c>
       <c r="M99">
-        <v>23.4672876</v>
+        <v>23.7092184</v>
       </c>
       <c r="N99">
-        <v>-19.1272876</v>
+        <v>-19.3692184</v>
       </c>
       <c r="O99">
-        <v>-4.590549024</v>
+        <v>-4.648612415999999</v>
       </c>
       <c r="P99">
-        <v>-14.536738576</v>
+        <v>-14.720605984</v>
       </c>
       <c r="Q99">
-        <v>-14.236738576</v>
+        <v>-14.420605984</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>6.487855840947376</v>
+        <v>9.708883761421063</v>
       </c>
       <c r="T99">
-        <v>31.652217984234</v>
+        <v>47.478326976351</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04438518919417002</v>
+        <v>0.04393227910035195</v>
       </c>
       <c r="W99">
-        <v>0.2253339723880147</v>
+        <v>0.225440768588137</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1849382883090417</v>
+        <v>0.1830511629181332</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.4151096284447957</v>
+        <v>0.4170096284447957</v>
       </c>
       <c r="C100">
-        <v>-41.8353694905173</v>
+        <v>-43.15354132458964</v>
       </c>
       <c r="D100">
-        <v>57.08263050948268</v>
+        <v>56.79045867541036</v>
       </c>
       <c r="E100">
-        <v>82.148</v>
+        <v>83.17400000000001</v>
       </c>
       <c r="F100">
-        <v>100.548</v>
+        <v>101.574</v>
       </c>
       <c r="G100">
         <v>1.63</v>
@@ -9481,37 +9481,37 @@
         <v>4.34</v>
       </c>
       <c r="M100">
-        <v>23.7092184</v>
+        <v>23.9511492</v>
       </c>
       <c r="N100">
-        <v>-19.3692184</v>
+        <v>-19.6111492</v>
       </c>
       <c r="O100">
-        <v>-4.648612415999999</v>
+        <v>-4.706675808</v>
       </c>
       <c r="P100">
-        <v>-14.720605984</v>
+        <v>-14.904473392</v>
       </c>
       <c r="Q100">
-        <v>-14.420605984</v>
+        <v>-14.604473392</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>9.708883761421063</v>
+        <v>19.37196752284213</v>
       </c>
       <c r="T100">
-        <v>47.478326976351</v>
+        <v>94.956653952702</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04393227910035195</v>
+        <v>0.0434885187053989</v>
       </c>
       <c r="W100">
-        <v>0.225440768588137</v>
+        <v>0.2255454072892669</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1830511629181332</v>
+        <v>0.1812021612724954</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.4170096284447957</v>
-      </c>
-      <c r="C101">
-        <v>-43.15354132458964</v>
-      </c>
-      <c r="D101">
-        <v>56.79045867541036</v>
-      </c>
-      <c r="E101">
-        <v>83.17400000000001</v>
-      </c>
-      <c r="F101">
-        <v>101.574</v>
-      </c>
-      <c r="G101">
-        <v>1.63</v>
-      </c>
-      <c r="H101">
-        <v>84.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.64</v>
-      </c>
-      <c r="K101">
-        <v>0.2999999999999998</v>
-      </c>
-      <c r="L101">
-        <v>4.34</v>
-      </c>
-      <c r="M101">
-        <v>23.9511492</v>
-      </c>
-      <c r="N101">
-        <v>-19.6111492</v>
-      </c>
-      <c r="O101">
-        <v>-4.706675808</v>
-      </c>
-      <c r="P101">
-        <v>-14.904473392</v>
-      </c>
-      <c r="Q101">
-        <v>-14.604473392</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>19.37196752284213</v>
-      </c>
-      <c r="T101">
-        <v>94.956653952702</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0434885187053989</v>
-      </c>
-      <c r="W101">
-        <v>0.2255454072892669</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1812021612724954</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
